--- a/coffee-shop-sales-analysis.xlsx
+++ b/coffee-shop-sales-analysis.xlsx
@@ -5,19 +5,19 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skill Learning for Work\Microsoft Excel - Myskill\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46B5ACC-5124-4E28-9C6E-E46142EC5744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74F158C-4E68-442A-94CE-692C979C94C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8892" yWindow="3144" windowWidth="14148" windowHeight="9816" firstSheet="7" activeTab="7" xr2:uid="{B93AFFF8-824F-4751-AA2F-E3944B4C415D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="2" activeTab="2" xr2:uid="{B93AFFF8-824F-4751-AA2F-E3944B4C415D}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Pertanyaan" sheetId="2" r:id="rId1"/>
     <sheet name="02_Data_Kotor" sheetId="9" r:id="rId2"/>
-    <sheet name="02b_Log_Cleaning" sheetId="10" r:id="rId3"/>
+    <sheet name="02b_Log_Cleaning" sheetId="11" r:id="rId3"/>
     <sheet name="03_Data Bersih + Analisis" sheetId="1" r:id="rId4"/>
-    <sheet name="04_Pivot_Table" sheetId="3" r:id="rId5"/>
+    <sheet name="04_Pivot_Table" sheetId="3" state="hidden" r:id="rId5"/>
     <sheet name="05_Dashboard" sheetId="4" r:id="rId6"/>
     <sheet name="06_Jawaban + Rekomendasi" sheetId="6" r:id="rId7"/>
     <sheet name="07_Dokumentasi_Rumus" sheetId="5" r:id="rId8"/>
@@ -30,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -500,6 +500,841 @@
     <t>Rekomendasi Aksi (Action Plan)</t>
   </si>
   <si>
+    <t>Berapa rata-rata nilai penjualan setiap transaksi? Tentukan juga apakah rata-rata yang kamu gunakan adalah rata-rata nilai transaksi atau rata-rata unit terjual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berapa total pendapatan dari seluruh produk berkategori Minuman? </t>
+  </si>
+  <si>
+    <t>22,000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MINUMAN</t>
+  </si>
+  <si>
+    <t>Chocolate cake</t>
+  </si>
+  <si>
+    <t>tunai</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>makanan</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>Rp 22.000</t>
+  </si>
+  <si>
+    <t>ord031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croissant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD028 </t>
+  </si>
+  <si>
+    <t>Choco Cake</t>
+  </si>
+  <si>
+    <t>3 pcs</t>
+  </si>
+  <si>
+    <t>minuman</t>
+  </si>
+  <si>
+    <t>Rp32.000</t>
+  </si>
+  <si>
+    <t>Cappucino</t>
+  </si>
+  <si>
+    <t>04 Okt 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minuman </t>
+  </si>
+  <si>
+    <t>Es Kopi  Susu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latte </t>
+  </si>
+  <si>
+    <t>matcha latte</t>
+  </si>
+  <si>
+    <t>americano</t>
+  </si>
+  <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>MAKANAN</t>
+  </si>
+  <si>
+    <t>Capuccino</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>es kopi susu</t>
+  </si>
+  <si>
+    <t>DEBIT</t>
+  </si>
+  <si>
+    <t>Chicken sandwich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LATTE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makanan </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Americano</t>
+  </si>
+  <si>
+    <t>Matcha latte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRIS </t>
+  </si>
+  <si>
+    <t>croissant</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>latte</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>qris</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Menu Kurang Laku:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chocolate Cake lemah di unit (9) dan pendapatan (Rp 198.000). Chicken Sandwich unitnya rendah (9), tapi pendapatannya lebih sehat (Rp 288.000).</t>
+    </r>
+  </si>
+  <si>
+    <t>ASUMSI &amp; KETERBATASAN ANALISIS</t>
+  </si>
+  <si>
+    <t>Rekomendasi bisnis bersifat awal (preliminary) dan perlu divalidasi dengan data historis yang lebih panjang (minimal 1-3 bulan).</t>
+  </si>
+  <si>
+    <t>Satu baris pesanan (order) diasumsikan hanya berisi satu jenis menu, sehingga pola pembelian bersamaan (analisis keranjang belanja) tidak dapat dianalisis dari data ini.</t>
+  </si>
+  <si>
+    <t>Analisis didasarkan pada 50 transaksi selama 10 hari (1-10 Oktober 2026).</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Rata-Rata (SUMIF/COUNTIF)</t>
+  </si>
+  <si>
+    <t>Maksimal (Unit)</t>
+  </si>
+  <si>
+    <t>Minimal (Unit)</t>
+  </si>
+  <si>
+    <t>Rata-Rata (Unit</t>
+  </si>
+  <si>
+    <t>Nilai Unit</t>
+  </si>
+  <si>
+    <t>Statistik Nilai Transaksi Keseluruhan</t>
+  </si>
+  <si>
+    <t>Rekapitulasi Total Unit Terjual per Menu</t>
+  </si>
+  <si>
+    <t>Statistik Kuantitas per Transaksi</t>
+  </si>
+  <si>
+    <t>Ringkasan</t>
+  </si>
+  <si>
+    <t>Mengambil Daftar Menu Unik</t>
+  </si>
+  <si>
+    <t>=UNIQUE(C4:C53)</t>
+  </si>
+  <si>
+    <t>=SUMIF(D4:D53, "Minuman", H4:H53)</t>
+  </si>
+  <si>
+    <t>Nilai Transaksi</t>
+  </si>
+  <si>
+    <t>=SUMIFS(H4:H53, D4:D53, "Minuman")</t>
+  </si>
+  <si>
+    <t>=IF(D4:D53="Minuman", H4:H53, 0)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(F4:F53)</t>
+  </si>
+  <si>
+    <t>=COUNTA(A4:A53)</t>
+  </si>
+  <si>
+    <t>=ROUND(AVERAGE(H4:H53), -3)</t>
+  </si>
+  <si>
+    <t>=MAXIFS(H4:H53, D4:D53, "Minuman")</t>
+  </si>
+  <si>
+    <t>QR Code</t>
+  </si>
+  <si>
+    <t>debit card</t>
+  </si>
+  <si>
+    <t>satu</t>
+  </si>
+  <si>
+    <t>Kartu Debit</t>
+  </si>
+  <si>
+    <t>dua</t>
+  </si>
+  <si>
+    <t>Sheet 03 dan seterusnya dibangun dari data yang sudah melewati langkah di atas.</t>
+  </si>
+  <si>
+    <t>Format tanggal "03/10/2026" dibaca sebagai dd/mm/yyyy (3 Oktober), konsisten dengan urutan order pada hari yang sama.</t>
+  </si>
+  <si>
+    <t>ORD038 (40 unit) dianggap salah ketik dari 4 unit. Ini satu-satunya koreksi berbasis asumsi; koreksi lain dapat dibuktikan langsung dari data.</t>
+  </si>
+  <si>
+    <t>E. Catatan Asumsi</t>
+  </si>
+  <si>
+    <t>Verifikasi: 50 baris, 8 menu, 2 kategori, 3 metode bayar, tanggal 01-10 Oktober 2026, tanpa sel kosong.</t>
+  </si>
+  <si>
+    <t>Bersihkan jumlah_terjual (teks/kata -&gt; angka), lalu tangani outlier ORD038.</t>
+  </si>
+  <si>
+    <t>Bersihkan harga_satuan (angka), lalu isi yang kosong dari harga menu yang sama.</t>
+  </si>
+  <si>
+    <t>Ubah tanggal teks ke format tanggal; isi tanggal kosong dari baris tetangga.</t>
+  </si>
+  <si>
+    <t>Samakan metode_pembayaran memakai kamus.</t>
+  </si>
+  <si>
+    <t>Rapikan nama_menu dan kategori (TRIM, PROPER), lalu terapkan kamus alias.</t>
+  </si>
+  <si>
+    <t>Hapus duplikat (Remove Duplicates pada seluruh kolom) -&gt; 53 menjadi 50 baris.</t>
+  </si>
+  <si>
+    <t>Rapikan order_id (TRIM, UPPER).</t>
+  </si>
+  <si>
+    <t>Salin 02_Data_Kotor ke area kerja baru (jangan timpa data mentah).</t>
+  </si>
+  <si>
+    <t>D. Urutan Pengerjaan yang Disarankan</t>
+  </si>
+  <si>
+    <t>debit / DEBIT</t>
+  </si>
+  <si>
+    <t>Cash / cash / tunai</t>
+  </si>
+  <si>
+    <t>qris / QRIS</t>
+  </si>
+  <si>
+    <t>Nilai Baku</t>
+  </si>
+  <si>
+    <t>Nilai Kotor</t>
+  </si>
+  <si>
+    <t>Kolom</t>
+  </si>
+  <si>
+    <t>Hanya ada 3 metode bayar; semua variasi punya makna yang sama.</t>
+  </si>
+  <si>
+    <t>TRIM, PROPER, Find &amp; Replace</t>
+  </si>
+  <si>
+    <t>Samakan ke 3 nilai baku: QRIS, Tunai, Debit lewat kamus (bagian C).</t>
+  </si>
+  <si>
+    <t>qris, QR Code -&gt; QRIS; Cash, cash -&gt; Tunai; debit, Kartu Debit, debit card -&gt; Debit</t>
+  </si>
+  <si>
+    <t>10 sel</t>
+  </si>
+  <si>
+    <t>Variasi penulisan</t>
+  </si>
+  <si>
+    <t>49 order lain berkisar 1-6 unit; 40 paling mungkin salah ketik (angka 0 berlebih). Jika ragu, konfirmasi ke kasir.</t>
+  </si>
+  <si>
+    <t>Filter / Conditional Formatting, lalu edit manual</t>
+  </si>
+  <si>
+    <t>Koreksi menjadi 4 dan tandai sebagai ASUMSI.</t>
+  </si>
+  <si>
+    <t>ORD038: 40 -&gt; 4</t>
+  </si>
+  <si>
+    <t>1 sel</t>
+  </si>
+  <si>
+    <t>Outlier</t>
+  </si>
+  <si>
+    <t>Kata bilangan dan satuan jelas maknanya, sehingga dapat diterjemahkan tanpa menebak.</t>
+  </si>
+  <si>
+    <t>SUBSTITUTE, VALUE, Find &amp; Replace</t>
+  </si>
+  <si>
+    <t>Buang teks satuan, ubah kata menjadi angka, ubah ke bilangan.</t>
+  </si>
+  <si>
+    <t>"3 pcs" -&gt; 3; "2" -&gt; 2; dua -&gt; 2; satu -&gt; 1</t>
+  </si>
+  <si>
+    <t>4 sel</t>
+  </si>
+  <si>
+    <t>Berupa teks atau kata</t>
+  </si>
+  <si>
+    <t>Setiap menu punya satu harga tetap di seluruh data, jadi aman dipulihkan.</t>
+  </si>
+  <si>
+    <t>INDEX-MATCH / VLOOKUP</t>
+  </si>
+  <si>
+    <t>Isi dengan harga menu yang sama di baris lain.</t>
+  </si>
+  <si>
+    <t>ORD029 (Latte) -&gt; 25000; ORD044 (Matcha Latte) -&gt; 28000</t>
+  </si>
+  <si>
+    <t>2 sel</t>
+  </si>
+  <si>
+    <t>Kosong</t>
+  </si>
+  <si>
+    <t>Harga dalam Rupiah utuh tanpa desimal; titik/koma di sini pemisah ribuan.</t>
+  </si>
+  <si>
+    <t>SUBSTITUTE, VALUE</t>
+  </si>
+  <si>
+    <t>Buang "Rp", spasi, titik, koma, lalu ubah ke angka.</t>
+  </si>
+  <si>
+    <t>Rp32.000 -&gt; 32000; 25.000 -&gt; 25000; 22,000 -&gt; 22000</t>
+  </si>
+  <si>
+    <t>6 sel</t>
+  </si>
+  <si>
+    <t>Tersimpan sebagai teks atau berformat Rp/titik/koma</t>
+  </si>
+  <si>
+    <t>Hanya ada 2 kategori baku: Makanan dan Minuman.</t>
+  </si>
+  <si>
+    <t>TRIM, PROPER</t>
+  </si>
+  <si>
+    <t>Hapus spasi dan samakan huruf.</t>
+  </si>
+  <si>
+    <t>MAKANAN -&gt; Makanan; "Minuman " -&gt; Minuman</t>
+  </si>
+  <si>
+    <t>7 sel</t>
+  </si>
+  <si>
+    <t>Huruf besar/kecil dan spasi di akhir</t>
+  </si>
+  <si>
+    <t>Daftar menu baku ada 8 item. Alias dipetakan ke menu yang jelas harga dan kategorinya sama.</t>
+  </si>
+  <si>
+    <t>Rapikan spasi dan huruf, lalu samakan alias lewat kamus (bagian C).</t>
+  </si>
+  <si>
+    <t>latte, LATTE  -&gt; Latte; Capuccino -&gt; Cappuccino; Choco Cake -&gt; Chocolate Cake</t>
+  </si>
+  <si>
+    <t>16 sel</t>
+  </si>
+  <si>
+    <t>Huruf besar/kecil, spasi, typo, dan alias</t>
+  </si>
+  <si>
+    <t>Order tercatat urut; ORD042 dan ORD044 sama-sama 09/10/2026, sehingga ORD043 pasti di hari yang sama.</t>
+  </si>
+  <si>
+    <t>Isi manual / rumus</t>
+  </si>
+  <si>
+    <t>Isi dengan tanggal baris sebelum dan sesudahnya.</t>
+  </si>
+  <si>
+    <t>ORD043: (kosong) -&gt; 09/10/2026</t>
+  </si>
+  <si>
+    <t>Format dd/mm/yyyy mengikuti kebiasaan Indonesia dan cocok dengan tanggal order di sekitarnya (urut per hari).</t>
+  </si>
+  <si>
+    <t>DATEVALUE, Text to Columns, Find &amp; Replace (Okt -&gt; Oct)</t>
+  </si>
+  <si>
+    <t>Ubah ke format tanggal dd/mm/yyyy.</t>
+  </si>
+  <si>
+    <t>03/10/2026; 04 Okt 2026; 2026-10-07 -&gt; tanggal sebenarnya</t>
+  </si>
+  <si>
+    <t>3 sel</t>
+  </si>
+  <si>
+    <t>Tersimpan sebagai teks dengan format berbeda</t>
+  </si>
+  <si>
+    <t>order_id sama dan seluruh kolom identik, jadi merupakan pencatatan ganda. Dibuktikan setelah order_id dirapikan.</t>
+  </si>
+  <si>
+    <t>Remove Duplicates</t>
+  </si>
+  <si>
+    <t>Hapus kemunculan kedua, simpan yang pertama.</t>
+  </si>
+  <si>
+    <t>ORD007, ORD023, ORD045 muncul 2 kali</t>
+  </si>
+  <si>
+    <t>3 baris</t>
+  </si>
+  <si>
+    <t>Baris duplikat persis</t>
+  </si>
+  <si>
+    <t>Semua kolom</t>
+  </si>
+  <si>
+    <t>ID harus seragam sebelum dipakai sebagai kunci duplikat.</t>
+  </si>
+  <si>
+    <t>TRIM, UPPER</t>
+  </si>
+  <si>
+    <t>Hapus spasi, ubah ke huruf besar. Dikerjakan PERTAMA agar duplikat terdeteksi.</t>
+  </si>
+  <si>
+    <t>Huruf kecil dan spasi di akhir</t>
+  </si>
+  <si>
+    <t>Dasar Keputusan</t>
+  </si>
+  <si>
+    <t>Alat Excel</t>
+  </si>
+  <si>
+    <t>Tindakan</t>
+  </si>
+  <si>
+    <t>Jumlah</t>
+  </si>
+  <si>
+    <t>Masalah</t>
+  </si>
+  <si>
+    <t>B. Daftar Masalah dan Tindakan</t>
+  </si>
+  <si>
+    <t>Baris data bersih (sesuai Table_Penjualan)</t>
+  </si>
+  <si>
+    <t>Baris duplikat dihapus</t>
+  </si>
+  <si>
+    <t>Baris data kotor</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>A. Rekonsiliasi Jumlah Baris</t>
+  </si>
+  <si>
+    <t>LOG CLEANING - DATA PENJUALAN KEDAI KOPI "DUMMY"</t>
+  </si>
+  <si>
+    <t>=E4*F4</t>
+  </si>
+  <si>
+    <t>=MIN(K12:K19)</t>
+  </si>
+  <si>
+    <t>=IF(K12=MAX($K$12:$K$19), J12, "")</t>
+  </si>
+  <si>
+    <t>=INDEX(J12:J19, MATCH(MAX(K12:K19), K12:K19, 0))</t>
+  </si>
+  <si>
+    <t>=XLOOKUP(MAX(K12:K19), K12:K19, J12:J19)</t>
+  </si>
+  <si>
+    <t>Mengecek JIKA Minuman DAN dibayar pakai QRIS.</t>
+  </si>
+  <si>
+    <t>=SUMIF(D4:D53,"Makanan",H4:H53)/COUNTIF(D4:D53,"Makanan")</t>
+  </si>
+  <si>
+    <t>Statistik Nilai Transaksi per Kategori</t>
+  </si>
+  <si>
+    <t>=SUMPRODUCT((C4:C53=$J12)*F4:F53)</t>
+  </si>
+  <si>
+    <t>Menjumlahkan unit terjual khusus untuk menu yang disebut di sel J12.</t>
+  </si>
+  <si>
+    <t>=IF(AND(D4="Minuman", G4="QRIS"), "Ya", "Tidak")</t>
+  </si>
+  <si>
+    <t>Mencari Angka Terendah</t>
+  </si>
+  <si>
+    <t>=MAX(K12:K19)</t>
+  </si>
+  <si>
+    <t>=MINIFS(H4:H53, D4:D53, "Makanan")</t>
+  </si>
+  <si>
+    <t>=COUNT(H4:H53)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(H4:H53)</t>
+  </si>
+  <si>
+    <t>Mengalikan harga dengan jumlah di baris yang sama.</t>
+  </si>
+  <si>
+    <t>Rata-Rata (AVERAGEIFS)</t>
+  </si>
+  <si>
+    <t>Analisis Tambahan (MINIFS, MAXIFS, AVERAGEIFS)</t>
+  </si>
+  <si>
+    <t>=AVERAGEIFS(H4:H53, D4:D53, "Makanan")</t>
+  </si>
+  <si>
+    <t>Total Pendapatan (Slicer)</t>
+  </si>
+  <si>
+    <t>Jumlah Transaksi (Slicer)</t>
+  </si>
+  <si>
+    <t>Item Terjual (Slicer)</t>
+  </si>
+  <si>
+    <t>Rata-Rata per Transaksi (Slicer)</t>
+  </si>
+  <si>
+    <t>Penjualan Unit Tertinggi</t>
+  </si>
+  <si>
+    <t>Penjualan Unit Terendah</t>
+  </si>
+  <si>
+    <t>Penjualan Unit Rata-Rata</t>
+  </si>
+  <si>
+    <t>Dashboard &amp; Data Interaktif</t>
+  </si>
+  <si>
+    <t>Mengambil Data dari Pivot (GETPIVOTDATA)</t>
+  </si>
+  <si>
+    <t>Mencegah Error saat Slicer Kosong (IFERROR)</t>
+  </si>
+  <si>
+    <t>Membuat Tabel Ringkasan Dinamis</t>
+  </si>
+  <si>
+    <t>=SUMIF($J$12:$J$19, J23, $K$12:$K$19)</t>
+  </si>
+  <si>
+    <t>=IFERROR(GETPIVOTDATA(...), 0)</t>
+  </si>
+  <si>
+    <t>=GETPIVOTDATA("Sum of nilai_transaksi",'04_Pivot_Table'!$D$1)</t>
+  </si>
+  <si>
+    <t>Membungkus rumus GETPIVOTDATA agar menampilkan angka 0 (bukan #REF!) jika filter Slicer tidak menemukan data.</t>
+  </si>
+  <si>
+    <t>Menghitung rata-rata dengan membagi total nilai dengan jumlah transaksi.</t>
+  </si>
+  <si>
+    <t>Mencari transaksi termahal khusus Minuman.</t>
+  </si>
+  <si>
+    <t>Membulatkan rata-rata ke ribuan terdekat (misal: 57.560 jadi 58.000).</t>
+  </si>
+  <si>
+    <t>Menghitung rata-rata jumlah barang yang dibeli per transaksi (2,48).</t>
+  </si>
+  <si>
+    <t>Mengambil nilai spesifik dari PivotTable secara dinamis.</t>
+  </si>
+  <si>
+    <t>Menjumlahkan data berdasarkan nama menu yang dipilih pada dropdown di tabel ringkasan.</t>
+  </si>
+  <si>
+    <t>Menghitung Data Tidak Kosong</t>
+  </si>
+  <si>
+    <t>Total Pendapatan via IF</t>
+  </si>
+  <si>
+    <t>Rujukan Lanjutan</t>
+  </si>
+  <si>
+    <t>Menautkan Jawaban ke Sheet Lain</t>
+  </si>
+  <si>
+    <t>Mengambil Total dari Tabel (Structured Ref)</t>
+  </si>
+  <si>
+    <t>='03_Data Bersih + Analisis'!O6</t>
+  </si>
+  <si>
+    <t>=Table2[[#Totals],[Minuman]]</t>
+  </si>
+  <si>
+    <t>Mengambil nilai dari sheet lain (agar jawaban di laporan otomatis ter-update tanpa ketik manual).</t>
+  </si>
+  <si>
+    <t>Mengambil angka dari baris "Total" spesifik pada kolom "Minuman" di tabel. Sangat berguna jika baris data bertambah.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Es Kopi Susu Menjadi Kontributor Utama:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Terjual 28 unit, menyumbang porsi terbesar pendapatan minuman.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Jaga Stok &amp; Loyalitas: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pastikan ketersediaan bahan baku "Es Kopi Susu" selalu aman. Buat program loyalitas (misal: Buy 5 Get 1 Free) khusus "Es Kopi Susu" untuk mempertahankan pelanggan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Minuman Mendominasi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pendapatan Minuman (Rp 2,112,000) sekitar 2,8x lipat Makanan (Rp 766,000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strategi Bundling (Perlu Diuji Coba):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Buat paket hemat (Kopi + Croissant) untuk "mengangkat" penjualan makanan yang masih rendah. (Catatan: Data saat ini belum menunjukkan pola pembelian bersamaan, sehingga promo ini perlu diuji efektivitasnya).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rata-rata Belanja:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pelanggan belanja Rp 57,560 per transaksi. Pelanggan rata-rata membeli 2,7 gelas minuman per transaksi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upselling:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tawarkan topping tambahan (extra shot / oat milk) atau camilan. (Contoh: Penambahan 1 item seharga Rp 7.500 dapat menaikkan rata-rata transaksi menjadi Rp 65.000+).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Metode Pembayaran Terbanyak:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> QRIS digunakan pada 22 dari 50 transaksi (44%).</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -544,299 +1379,6 @@
     </r>
   </si>
   <si>
-    <t>Berapa rata-rata nilai penjualan setiap transaksi? Tentukan juga apakah rata-rata yang kamu gunakan adalah rata-rata nilai transaksi atau rata-rata unit terjual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berapa total pendapatan dari seluruh produk berkategori Minuman? </t>
-  </si>
-  <si>
-    <t>22,000</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MINUMAN</t>
-  </si>
-  <si>
-    <t>Chocolate cake</t>
-  </si>
-  <si>
-    <t>tunai</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>makanan</t>
-  </si>
-  <si>
-    <t>2026-10-07</t>
-  </si>
-  <si>
-    <t>Rp 22.000</t>
-  </si>
-  <si>
-    <t>ord031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croissant </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORD028 </t>
-  </si>
-  <si>
-    <t>Choco Cake</t>
-  </si>
-  <si>
-    <t>3 pcs</t>
-  </si>
-  <si>
-    <t>minuman</t>
-  </si>
-  <si>
-    <t>Rp32.000</t>
-  </si>
-  <si>
-    <t>Cappucino</t>
-  </si>
-  <si>
-    <t>04 Okt 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minuman </t>
-  </si>
-  <si>
-    <t>Es Kopi  Susu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latte </t>
-  </si>
-  <si>
-    <t>matcha latte</t>
-  </si>
-  <si>
-    <t>americano</t>
-  </si>
-  <si>
-    <t>03/10/2026</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>MAKANAN</t>
-  </si>
-  <si>
-    <t>Capuccino</t>
-  </si>
-  <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>es kopi susu</t>
-  </si>
-  <si>
-    <t>DEBIT</t>
-  </si>
-  <si>
-    <t>Chicken sandwich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LATTE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makanan </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Americano</t>
-  </si>
-  <si>
-    <t>Matcha latte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QRIS </t>
-  </si>
-  <si>
-    <t>croissant</t>
-  </si>
-  <si>
-    <t>debit</t>
-  </si>
-  <si>
-    <t>latte</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>qris</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Es Kopi Susu Menjadi Kontributor Utama:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Terjual 28 unit, menyumbang porsi terbesar pendapatan minuman.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Jaga Stok &amp; Loyalitas: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pastikan ketersediaan bahan baku "Es Kopi Susu" selalu aman. Buat program loyalitas (misal: Buy 5 Get 1 Free) khusus "Es Kopi Susu" untuk mempertahankan pelanggan.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Minuman Mendominasi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pendapatan Minuman (Rp 2,112,000) sekitar 2,8x lipat Makanan (Rp 766,000).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Strategi Bundling (Perlu Diuji Coba):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Buat paket hemat (Kopi + Croissant) untuk "mengangkat" penjualan makanan yang masih rendah. (Catatan: Data saat ini belum menunjukkan pola pembelian bersamaan, sehingga promo ini perlu diuji efektivitasnya).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upselling:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tawarkan topping tambahan (extra shot / oat milk) atau camilan. (Contoh: Penambahan 1 item seharga Rp 7.500 dapat menaikkan rata-rata transaksi menjadi Rp 65.000+).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rata-rata Belanja:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pelanggan belanja Rp 57,560 per transaksi. Pelanggan rata-rata membeli 2,7 gelas minuman per transaksi.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Metode Pembayaran Terbanyak:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> QRIS digunakan pada 22 dari 50 transaksi (44%).</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -864,428 +1406,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Menu Kurang Laku:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Chocolate Cake lemah di unit (9) dan pendapatan (Rp 198.000). Chicken Sandwich unitnya rendah (9), tapi pendapatannya lebih sehat (Rp 288.000).</t>
-    </r>
-  </si>
-  <si>
-    <t>ASUMSI &amp; KETERBATASAN ANALISIS</t>
-  </si>
-  <si>
-    <t>Rekomendasi bisnis bersifat awal (preliminary) dan perlu divalidasi dengan data historis yang lebih panjang (minimal 1-3 bulan).</t>
-  </si>
-  <si>
-    <t>Satu baris pesanan (order) diasumsikan hanya berisi satu jenis menu, sehingga pola pembelian bersamaan (analisis keranjang belanja) tidak dapat dianalisis dari data ini.</t>
-  </si>
-  <si>
-    <t>Analisis didasarkan pada 50 transaksi selama 10 hari (1-10 Oktober 2026).</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Rata-Rata (SUMIF/COUNTIF)</t>
-  </si>
-  <si>
-    <t>Maksimal (Unit)</t>
-  </si>
-  <si>
-    <t>Minimal (Unit)</t>
-  </si>
-  <si>
-    <t>Rata-Rata (Unit</t>
-  </si>
-  <si>
-    <t>Nilai Unit</t>
-  </si>
-  <si>
-    <t>Statistik Nilai Transaksi Keseluruhan</t>
-  </si>
-  <si>
-    <t>Rekapitulasi Total Unit Terjual per Menu</t>
-  </si>
-  <si>
-    <t>Statistik Kuantitas per Transaksi</t>
-  </si>
-  <si>
-    <t>Ringkasan</t>
-  </si>
-  <si>
-    <t>Mengambil Daftar Menu Unik</t>
-  </si>
-  <si>
-    <t>=UNIQUE(C4:C53)</t>
-  </si>
-  <si>
-    <t>=SUMIF(D4:D53, "Minuman", H4:H53)</t>
-  </si>
-  <si>
-    <t>Nilai Transaksi</t>
-  </si>
-  <si>
-    <t>=SUMIFS(H4:H53, D4:D53, "Minuman")</t>
-  </si>
-  <si>
-    <t>=IF(D4:D53="Minuman", H4:H53, 0)</t>
-  </si>
-  <si>
-    <t>=AVERAGE(F4:F53)</t>
-  </si>
-  <si>
-    <t>=COUNTA(A4:A53)</t>
-  </si>
-  <si>
-    <t>=ROUND(AVERAGE(H4:H53), -3)</t>
-  </si>
-  <si>
-    <t>=MAXIFS(H4:H53, D4:D53, "Minuman")</t>
-  </si>
-  <si>
-    <t>QR Code</t>
-  </si>
-  <si>
-    <t>debit card</t>
-  </si>
-  <si>
-    <t>satu</t>
-  </si>
-  <si>
-    <t>Kartu Debit</t>
-  </si>
-  <si>
-    <t>dua</t>
-  </si>
-  <si>
-    <t>Sheet 03 dan seterusnya dibangun dari data yang sudah melewati langkah di atas.</t>
-  </si>
-  <si>
-    <t>Format tanggal "03/10/2026" dibaca sebagai dd/mm/yyyy (3 Oktober), konsisten dengan urutan order pada hari yang sama.</t>
-  </si>
-  <si>
-    <t>ORD038 (40 unit) dianggap salah ketik dari 4 unit. Ini satu-satunya koreksi berbasis asumsi; koreksi lain dapat dibuktikan langsung dari data.</t>
-  </si>
-  <si>
-    <t>E. Catatan Asumsi</t>
-  </si>
-  <si>
-    <t>Verifikasi: 50 baris, 8 menu, 2 kategori, 3 metode bayar, tanggal 01-10 Oktober 2026, tanpa sel kosong.</t>
-  </si>
-  <si>
-    <t>Bersihkan jumlah_terjual (teks/kata -&gt; angka), lalu tangani outlier ORD038.</t>
-  </si>
-  <si>
-    <t>Bersihkan harga_satuan (angka), lalu isi yang kosong dari harga menu yang sama.</t>
-  </si>
-  <si>
-    <t>Ubah tanggal teks ke format tanggal; isi tanggal kosong dari baris tetangga.</t>
-  </si>
-  <si>
-    <t>Samakan metode_pembayaran memakai kamus.</t>
-  </si>
-  <si>
-    <t>Rapikan nama_menu dan kategori (TRIM, PROPER), lalu terapkan kamus alias.</t>
-  </si>
-  <si>
-    <t>Hapus duplikat (Remove Duplicates pada seluruh kolom) -&gt; 53 menjadi 50 baris.</t>
-  </si>
-  <si>
-    <t>Rapikan order_id (TRIM, UPPER).</t>
-  </si>
-  <si>
-    <t>Salin 02_Data_Kotor ke area kerja baru (jangan timpa data mentah).</t>
-  </si>
-  <si>
-    <t>D. Urutan Pengerjaan yang Disarankan</t>
-  </si>
-  <si>
-    <t>debit / DEBIT</t>
-  </si>
-  <si>
-    <t>Cash / cash / tunai</t>
-  </si>
-  <si>
-    <t>qris / QRIS</t>
-  </si>
-  <si>
-    <t>Nilai Baku</t>
-  </si>
-  <si>
-    <t>Nilai Kotor</t>
-  </si>
-  <si>
-    <t>Kolom</t>
-  </si>
-  <si>
-    <t>C. Kamus Standarisasi (Nilai Kotor -&gt; Nilai Baku)</t>
-  </si>
-  <si>
-    <t>Hanya ada 3 metode bayar; semua variasi punya makna yang sama.</t>
-  </si>
-  <si>
-    <t>TRIM, PROPER, Find &amp; Replace</t>
-  </si>
-  <si>
-    <t>Samakan ke 3 nilai baku: QRIS, Tunai, Debit lewat kamus (bagian C).</t>
-  </si>
-  <si>
-    <t>qris, QR Code -&gt; QRIS; Cash, cash -&gt; Tunai; debit, Kartu Debit, debit card -&gt; Debit</t>
-  </si>
-  <si>
-    <t>10 sel</t>
-  </si>
-  <si>
-    <t>Variasi penulisan</t>
-  </si>
-  <si>
-    <t>49 order lain berkisar 1-6 unit; 40 paling mungkin salah ketik (angka 0 berlebih). Jika ragu, konfirmasi ke kasir.</t>
-  </si>
-  <si>
-    <t>Filter / Conditional Formatting, lalu edit manual</t>
-  </si>
-  <si>
-    <t>Koreksi menjadi 4 dan tandai sebagai ASUMSI.</t>
-  </si>
-  <si>
-    <t>ORD038: 40 -&gt; 4</t>
-  </si>
-  <si>
-    <t>1 sel</t>
-  </si>
-  <si>
-    <t>Outlier</t>
-  </si>
-  <si>
-    <t>Kata bilangan dan satuan jelas maknanya, sehingga dapat diterjemahkan tanpa menebak.</t>
-  </si>
-  <si>
-    <t>SUBSTITUTE, VALUE, Find &amp; Replace</t>
-  </si>
-  <si>
-    <t>Buang teks satuan, ubah kata menjadi angka, ubah ke bilangan.</t>
-  </si>
-  <si>
-    <t>"3 pcs" -&gt; 3; "2" -&gt; 2; dua -&gt; 2; satu -&gt; 1</t>
-  </si>
-  <si>
-    <t>4 sel</t>
-  </si>
-  <si>
-    <t>Berupa teks atau kata</t>
-  </si>
-  <si>
-    <t>Setiap menu punya satu harga tetap di seluruh data, jadi aman dipulihkan.</t>
-  </si>
-  <si>
-    <t>INDEX-MATCH / VLOOKUP</t>
-  </si>
-  <si>
-    <t>Isi dengan harga menu yang sama di baris lain.</t>
-  </si>
-  <si>
-    <t>ORD029 (Latte) -&gt; 25000; ORD044 (Matcha Latte) -&gt; 28000</t>
-  </si>
-  <si>
-    <t>2 sel</t>
-  </si>
-  <si>
-    <t>Kosong</t>
-  </si>
-  <si>
-    <t>Harga dalam Rupiah utuh tanpa desimal; titik/koma di sini pemisah ribuan.</t>
-  </si>
-  <si>
-    <t>SUBSTITUTE, VALUE</t>
-  </si>
-  <si>
-    <t>Buang "Rp", spasi, titik, koma, lalu ubah ke angka.</t>
-  </si>
-  <si>
-    <t>Rp32.000 -&gt; 32000; 25.000 -&gt; 25000; 22,000 -&gt; 22000</t>
-  </si>
-  <si>
-    <t>6 sel</t>
-  </si>
-  <si>
-    <t>Tersimpan sebagai teks atau berformat Rp/titik/koma</t>
-  </si>
-  <si>
-    <t>Hanya ada 2 kategori baku: Makanan dan Minuman.</t>
-  </si>
-  <si>
-    <t>TRIM, PROPER</t>
-  </si>
-  <si>
-    <t>Hapus spasi dan samakan huruf.</t>
-  </si>
-  <si>
-    <t>MAKANAN -&gt; Makanan; "Minuman " -&gt; Minuman</t>
-  </si>
-  <si>
-    <t>7 sel</t>
-  </si>
-  <si>
-    <t>Huruf besar/kecil dan spasi di akhir</t>
-  </si>
-  <si>
-    <t>Daftar menu baku ada 8 item. Alias dipetakan ke menu yang jelas harga dan kategorinya sama.</t>
-  </si>
-  <si>
-    <t>Rapikan spasi dan huruf, lalu samakan alias lewat kamus (bagian C).</t>
-  </si>
-  <si>
-    <t>latte, LATTE  -&gt; Latte; Capuccino -&gt; Cappuccino; Choco Cake -&gt; Chocolate Cake</t>
-  </si>
-  <si>
-    <t>16 sel</t>
-  </si>
-  <si>
-    <t>Huruf besar/kecil, spasi, typo, dan alias</t>
-  </si>
-  <si>
-    <t>Order tercatat urut; ORD042 dan ORD044 sama-sama 09/10/2026, sehingga ORD043 pasti di hari yang sama.</t>
-  </si>
-  <si>
-    <t>Isi manual / rumus</t>
-  </si>
-  <si>
-    <t>Isi dengan tanggal baris sebelum dan sesudahnya.</t>
-  </si>
-  <si>
-    <t>ORD043: (kosong) -&gt; 09/10/2026</t>
-  </si>
-  <si>
-    <t>Format dd/mm/yyyy mengikuti kebiasaan Indonesia dan cocok dengan tanggal order di sekitarnya (urut per hari).</t>
-  </si>
-  <si>
-    <t>DATEVALUE, Text to Columns, Find &amp; Replace (Okt -&gt; Oct)</t>
-  </si>
-  <si>
-    <t>Ubah ke format tanggal dd/mm/yyyy.</t>
-  </si>
-  <si>
-    <t>03/10/2026; 04 Okt 2026; 2026-10-07 -&gt; tanggal sebenarnya</t>
-  </si>
-  <si>
-    <t>3 sel</t>
-  </si>
-  <si>
-    <t>Tersimpan sebagai teks dengan format berbeda</t>
-  </si>
-  <si>
-    <t>order_id sama dan seluruh kolom identik, jadi merupakan pencatatan ganda. Dibuktikan setelah order_id dirapikan.</t>
-  </si>
-  <si>
-    <t>Remove Duplicates</t>
-  </si>
-  <si>
-    <t>Hapus kemunculan kedua, simpan yang pertama.</t>
-  </si>
-  <si>
-    <t>ORD007, ORD023, ORD045 muncul 2 kali</t>
-  </si>
-  <si>
-    <t>3 baris</t>
-  </si>
-  <si>
-    <t>Baris duplikat persis</t>
-  </si>
-  <si>
-    <t>Semua kolom</t>
-  </si>
-  <si>
-    <t>ID harus seragam sebelum dipakai sebagai kunci duplikat.</t>
-  </si>
-  <si>
-    <t>TRIM, UPPER</t>
-  </si>
-  <si>
-    <t>Hapus spasi, ubah ke huruf besar. Dikerjakan PERTAMA agar duplikat terdeteksi.</t>
-  </si>
-  <si>
-    <t>ord031 -&gt; ORD031; "ORD028 " -&gt; ORD028</t>
-  </si>
-  <si>
-    <t>Huruf kecil dan spasi di akhir</t>
-  </si>
-  <si>
-    <t>Dasar Keputusan</t>
-  </si>
-  <si>
-    <t>Alat Excel</t>
-  </si>
-  <si>
-    <t>Tindakan</t>
-  </si>
-  <si>
-    <t>Contoh (sebelum -&gt; sesudah)</t>
-  </si>
-  <si>
-    <t>Jumlah</t>
-  </si>
-  <si>
-    <t>Masalah</t>
-  </si>
-  <si>
-    <t>B. Daftar Masalah dan Tindakan</t>
-  </si>
-  <si>
-    <t>Baris data bersih (sesuai Table_Penjualan)</t>
-  </si>
-  <si>
-    <t>Baris duplikat dihapus</t>
-  </si>
-  <si>
-    <t>Baris data kotor</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>A. Rekonsiliasi Jumlah Baris</t>
-  </si>
-  <si>
-    <t>LOG CLEANING - DATA PENJUALAN KEDAI KOPI "DUMMY"</t>
-  </si>
-  <si>
-    <t>=E4*F4</t>
-  </si>
-  <si>
-    <t>=MIN(K12:K19)</t>
-  </si>
-  <si>
-    <t>=IF(K12=MAX($K$12:$K$19), J12, "")</t>
-  </si>
-  <si>
-    <t>=INDEX(J12:J19, MATCH(MAX(K12:K19), K12:K19, 0))</t>
-  </si>
-  <si>
-    <t>=XLOOKUP(MAX(K12:K19), K12:K19, J12:J19)</t>
-  </si>
-  <si>
-    <t>Mengecek JIKA Minuman DAN dibayar pakai QRIS.</t>
-  </si>
-  <si>
-    <t>=SUMIF(D4:D53,"Makanan",H4:H53)/COUNTIF(D4:D53,"Makanan")</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1328,133 +1448,13 @@
     </r>
   </si>
   <si>
-    <t>Statistik Nilai Transaksi per Kategori</t>
-  </si>
-  <si>
-    <t>=SUMPRODUCT((C4:C53=$J12)*F4:F53)</t>
-  </si>
-  <si>
-    <t>Menjumlahkan unit terjual khusus untuk menu yang disebut di sel J12.</t>
-  </si>
-  <si>
-    <t>=IF(AND(D4="Minuman", G4="QRIS"), "Ya", "Tidak")</t>
-  </si>
-  <si>
-    <t>Mencari Angka Terendah</t>
-  </si>
-  <si>
-    <t>=MAX(K12:K19)</t>
-  </si>
-  <si>
-    <t>=MINIFS(H4:H53, D4:D53, "Makanan")</t>
-  </si>
-  <si>
-    <t>=COUNT(H4:H53)</t>
-  </si>
-  <si>
-    <t>=AVERAGE(H4:H53)</t>
-  </si>
-  <si>
-    <t>Mengalikan harga dengan jumlah di baris yang sama.</t>
-  </si>
-  <si>
-    <t>Rata-Rata (AVERAGEIFS)</t>
-  </si>
-  <si>
-    <t>Analisis Tambahan (MINIFS, MAXIFS, AVERAGEIFS)</t>
-  </si>
-  <si>
-    <t>=AVERAGEIFS(H4:H53, D4:D53, "Makanan")</t>
-  </si>
-  <si>
-    <t>Total Pendapatan (Slicer)</t>
-  </si>
-  <si>
-    <t>Jumlah Transaksi (Slicer)</t>
-  </si>
-  <si>
-    <t>Item Terjual (Slicer)</t>
-  </si>
-  <si>
-    <t>Rata-Rata per Transaksi (Slicer)</t>
-  </si>
-  <si>
-    <t>Penjualan Unit Tertinggi</t>
-  </si>
-  <si>
-    <t>Penjualan Unit Terendah</t>
-  </si>
-  <si>
-    <t>Penjualan Unit Rata-Rata</t>
-  </si>
-  <si>
-    <t>Dashboard &amp; Data Interaktif</t>
-  </si>
-  <si>
-    <t>Mengambil Data dari Pivot (GETPIVOTDATA)</t>
-  </si>
-  <si>
-    <t>Mencegah Error saat Slicer Kosong (IFERROR)</t>
-  </si>
-  <si>
-    <t>Membuat Tabel Ringkasan Dinamis</t>
-  </si>
-  <si>
-    <t>=SUMIF($J$12:$J$19, J23, $K$12:$K$19)</t>
-  </si>
-  <si>
-    <t>=IFERROR(GETPIVOTDATA(...), 0)</t>
-  </si>
-  <si>
-    <t>=GETPIVOTDATA("Sum of nilai_transaksi",'04_Pivot_Table'!$D$1)</t>
-  </si>
-  <si>
-    <t>Membungkus rumus GETPIVOTDATA agar menampilkan angka 0 (bukan #REF!) jika filter Slicer tidak menemukan data.</t>
-  </si>
-  <si>
-    <t>Menghitung rata-rata dengan membagi total nilai dengan jumlah transaksi.</t>
-  </si>
-  <si>
-    <t>Mencari transaksi termahal khusus Minuman.</t>
-  </si>
-  <si>
-    <t>Membulatkan rata-rata ke ribuan terdekat (misal: 57.560 jadi 58.000).</t>
-  </si>
-  <si>
-    <t>Menghitung rata-rata jumlah barang yang dibeli per transaksi (2,48).</t>
-  </si>
-  <si>
-    <t>Mengambil nilai spesifik dari PivotTable secara dinamis.</t>
-  </si>
-  <si>
-    <t>Menjumlahkan data berdasarkan nama menu yang dipilih pada dropdown di tabel ringkasan.</t>
-  </si>
-  <si>
-    <t>Menghitung Data Tidak Kosong</t>
-  </si>
-  <si>
-    <t>Total Pendapatan via IF</t>
-  </si>
-  <si>
-    <t>Rujukan Lanjutan</t>
-  </si>
-  <si>
-    <t>Menautkan Jawaban ke Sheet Lain</t>
-  </si>
-  <si>
-    <t>Mengambil Total dari Tabel (Structured Ref)</t>
-  </si>
-  <si>
-    <t>='03_Data Bersih + Analisis'!O6</t>
-  </si>
-  <si>
-    <t>=Table2[[#Totals],[Minuman]]</t>
-  </si>
-  <si>
-    <t>Mengambil nilai dari sheet lain (agar jawaban di laporan otomatis ter-update tanpa ketik manual).</t>
-  </si>
-  <si>
-    <t>Mengambil angka dari baris "Total" spesifik pada kolom "Minuman" di tabel. Sangat berguna jika baris data bertambah.</t>
+    <t>ord031 -&gt; ORD031; "ORD028" -&gt; ORD028</t>
+  </si>
+  <si>
+    <t>sebelum -&gt; sesudah</t>
+  </si>
+  <si>
+    <t>C. Nilai Kotor -&gt; Nilai Baku</t>
   </si>
 </sst>
 </file>
@@ -1466,12 +1466,12 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    <numFmt numFmtId="172" formatCode="&quot;Total Pendapatan&quot;\ &quot;Rp&quot;\ #,##0"/>
-    <numFmt numFmtId="173" formatCode="&quot;Jumlah Transaksi&quot;\ 0"/>
-    <numFmt numFmtId="174" formatCode="&quot;Item Terjual&quot;\ 0"/>
-    <numFmt numFmtId="175" formatCode="&quot;Rata-Rata per Transaksi&quot;\ &quot;Rp&quot;\ #,#00"/>
+    <numFmt numFmtId="168" formatCode="&quot;Total Pendapatan&quot;\ &quot;Rp&quot;\ #,##0"/>
+    <numFmt numFmtId="169" formatCode="&quot;Jumlah Transaksi&quot;\ 0"/>
+    <numFmt numFmtId="170" formatCode="&quot;Item Terjual&quot;\ 0"/>
+    <numFmt numFmtId="171" formatCode="&quot;Rata-Rata per Transaksi&quot;\ &quot;Rp&quot;\ #,#00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1512,14 +1512,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF0F1115"/>
       <name val="Calibri"/>
@@ -1548,12 +1540,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1568,30 +1554,10 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Calibri "/>
     </font>
     <font>
       <b/>
@@ -1600,6 +1566,84 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1652,7 +1696,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1909,12 +1953,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1971,7 +2107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1989,7 +2125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2037,16 +2173,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2055,7 +2191,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2071,44 +2207,41 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2131,60 +2264,129 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{659D0F69-23FA-4FBD-BAF1-391F0B172C48}"/>
   </cellStyles>
-  <dxfs count="144">
+  <dxfs count="121">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2204,249 +2406,639 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
+          <fgColor rgb="FF003366"/>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </left>
         <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </right>
         <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color rgb="FFBFBFBF"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF4B2E1E"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2473,6 +3065,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2486,6 +3079,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2499,29 +3093,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2535,38 +3107,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2580,217 +3121,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2886,7 +3216,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2900,7 +3229,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2914,7 +3242,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2928,7 +3255,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2942,6 +3268,206 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2989,8 +3515,211 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3001,23 +3730,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3033,6 +3745,39 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="dd\ mmm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -3344,10 +4089,20 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4B2E1E"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Kopi" pivot="0" table="0" count="2" xr9:uid="{CE243F44-6D59-4553-AF96-A5BC71C20E8D}">
-      <tableStyleElement type="headerRow" dxfId="70"/>
+      <tableStyleElement type="headerRow" dxfId="120"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3401,7 +4156,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable1</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable1</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -4152,7 +4907,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable3</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable3</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -4697,7 +5452,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable6</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable6</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -5237,7 +5992,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable5</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable5</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -5817,7 +6572,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable2</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable2</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -6357,7 +7112,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable4</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable4</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -6902,7 +7657,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable7</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable7</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
@@ -7117,9 +7872,6 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
           <a:ln>
             <a:solidFill>
               <a:srgbClr val="C69C6D"/>
@@ -7159,9 +7911,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
             <a:ln>
               <a:solidFill>
                 <a:srgbClr val="C69C6D"/>
@@ -7424,7 +8173,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Analisis-Penjualan-Kedai-Kopi-Sederhana.xlsx.xlsx]04_Pivot_Table!PivotTable9</c:name>
+    <c:name>[coffee-shop-sales-analysis.xlsx]04_Pivot_Table!PivotTable9</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -12673,8 +13422,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>587828</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="tanggal">
@@ -12697,7 +13446,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12751,8 +13500,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>609600</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="13" name="metode_pembayaran">
@@ -12775,7 +13524,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12963,6 +13712,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Total Pendapatan Rp 2,878,000</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800" b="1">
@@ -13250,6 +14000,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Jumlah Transaksi 50</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800" b="1">
@@ -13333,6 +14084,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Item Terjual 124</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800" b="1">
@@ -13416,6 +14168,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Rata-Rata per Transaksi Rp 57,560</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1800" b="1">
@@ -14003,351 +14756,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FD21C08-3B68-40AA-8ADE-3E903B1DF5B8}" name="PivotTable6" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="D7:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of jumlah_terjual" fld="5" baseField="3" baseItem="0" numFmtId="1"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="62">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="63">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9408B42-FFE1-40A4-866B-3527BD80D5A9}" name="PivotTable7" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A13:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="165" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of nilai_transaksi" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="60">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6056A3F-23C5-4E7D-A003-C461BFD54207}" name="PivotTable5" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="J4:K8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of order_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="64">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="3" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4374B3B3-BEBE-47E2-8582-4D9E542FF800}" name="PivotTable4" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4374B3B3-BEBE-47E2-8582-4D9E542FF800}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="G7:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -14407,7 +14816,7 @@
     <dataField name="Average of jumlah_terjual" fld="5" subtotal="average" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="65">
+    <format dxfId="83">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
@@ -14450,8 +14859,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8E560E2-CD55-430E-A5CE-DF9837E6C8EF}" name="PivotTable3" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8E560E2-CD55-430E-A5CE-DF9837E6C8EF}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="G1:H4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -14511,14 +14920,14 @@
     <dataField name="Average of nilai_transaksi" fld="7" subtotal="average" baseField="0" baseItem="1920052788"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="66">
+    <format dxfId="85">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="84">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14557,8 +14966,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C6A7F74-71B4-49A3-A519-CCD35D012813}" name="PivotTable9" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C6A7F74-71B4-49A3-A519-CCD35D012813}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="D13:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -14651,7 +15060,7 @@
     <dataField name="Sum of nilai_transaksi" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="59">
+    <format dxfId="86">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14708,8 +15117,255 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1139930-8EF3-4C08-BE62-0C09E68FEB36}" name="PivotTable2" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FD21C08-3B68-40AA-8ADE-3E903B1DF5B8}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="D7:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of jumlah_terjual" fld="5" baseField="3" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="88">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="87">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9408B42-FFE1-40A4-866B-3527BD80D5A9}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A13:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="165" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of nilai_transaksi" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="90">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="89">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1139930-8EF3-4C08-BE62-0C09E68FEB36}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="D1:E4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -14769,14 +15425,14 @@
     <dataField name="Sum of nilai_transaksi" fld="7" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="68">
+    <format dxfId="92">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="91">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14815,8 +15471,105 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6056A3F-23C5-4E7D-A003-C461BFD54207}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="J4:K8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of order_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="93">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05CF5101-5918-4C3B-979A-BF4704F629BD}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05CF5101-5918-4C3B-979A-BF4704F629BD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -15006,17 +15759,126 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{84755AD8-B8C6-4E5C-B91B-6FE88BF651DE}" name="Table_Penjualan" displayName="Table_Penjualan" ref="A3:H53" totalsRowShown="0" headerRowDxfId="143">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{662FD5BD-C0FD-4C03-90A5-96090E66CDA3}" name="Table1" displayName="Table1" ref="A4:B7" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="25" tableBorderDxfId="26" totalsRowBorderDxfId="24" headerRowCellStyle="Normal 2">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{B383A504-A6BF-4FAA-9FAF-C424E8916F78}" name="Keterangan" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{99016240-4E9D-4A88-A2F7-4889B1EAA3DD}" name="Jumlah" dataDxfId="2" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9FAE22C4-446B-4A13-A1CD-0DB87E8C10A0}" name="Table7" displayName="Table7" ref="A2:D5" totalsRowShown="0" dataDxfId="27">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F755DA5B-2F83-4385-BCC6-AD508E78DB3A}" name="No" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{8C7CC80E-A128-427F-BD1D-2BACBA719C93}" name="Tujuan/Kasus" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{F1B4465F-FE60-4FF7-B84A-D385948C37B0}" name="Rumus Excel" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{E32FFBC9-7F4D-4672-8A93-DD6EEA3046C8}" name="Penjelasan Singkat" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1D6DB6B6-FE1D-41FB-A522-2B62CD7C9B8B}" name="Table79" displayName="Table79" ref="A9:D14" totalsRowShown="0" headerRowDxfId="77" dataDxfId="32">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{36FDD706-320A-4AF4-9DDB-14628E07A8C6}" name="No" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{259F1008-7A90-4BC6-A8CF-3EC2792378BE}" name="Tujuan/Kasus" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{75772802-8B13-4D98-A130-1B1DB609A539}" name="Rumus Excel" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{F29DA025-DBE7-4483-84CB-CEED80B7283F}" name="Penjelasan Singkat" dataDxfId="33"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B4D75F84-B8C0-48AC-A1B4-291BA76FEB55}" name="Table9" displayName="Table9" ref="A18:D22" totalsRowShown="0" headerRowDxfId="76" dataDxfId="37" headerRowBorderDxfId="75" tableBorderDxfId="74" totalsRowBorderDxfId="73">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{625B4CEF-1E36-4695-8BA9-FA81F4574EBE}" name="No" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{C999B219-67E3-4A4F-8146-2F3228023EC0}" name="Tujuan/Kasus" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{7BEBD530-1C27-4A06-B9C4-4750E9600B1D}" name="Rumus Excel" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{FDD7E416-9455-4BB4-9E28-158698304E8A}" name="Penjelasan Singkat" dataDxfId="38"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2D3EB2AF-BFFE-43D6-AAA3-75CDA71579F1}" name="Table10" displayName="Table10" ref="A26:D31" totalsRowShown="0" headerRowDxfId="72" dataDxfId="42" headerRowBorderDxfId="71" tableBorderDxfId="70">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{3E335885-447E-43F5-AE72-08BEF8FA6E7F}" name="No" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{F3D3347C-AE9F-4B5D-8892-43B69E298AFE}" name="Tujuan/Kasus" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{55F3CDC3-7757-45F3-A3EF-5EA9942A1B50}" name="Rumus Excel" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{C58994CB-6CD9-4EAF-A7EA-6BEB7B73571A}" name="Penjelasan Singkat" dataDxfId="43"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2B43984E-C349-413A-9BFB-A7F32F00FFF1}" name="Table11" displayName="Table11" ref="A35:D39" totalsRowShown="0" headerRowDxfId="69" dataDxfId="47" headerRowBorderDxfId="68" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{29351D3F-CA74-4483-8825-DBF8EC540217}" name="No" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{A1DEA393-6C32-4DDD-9410-B141231A2055}" name="Tujuan/Kasus" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{A80EEEA2-1401-487A-8432-AE1D5043050C}" name="Rumus Excel" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{01BF720C-419F-44FE-8980-2242B99E4B1F}" name="Penjelasan Singkat" dataDxfId="48"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{188AC7E4-A225-40B6-A5D6-F5E902BF1042}" name="Table3" displayName="Table3" ref="A43:D46" totalsRowShown="0" headerRowDxfId="65" dataDxfId="52" headerRowBorderDxfId="64" tableBorderDxfId="63" totalsRowBorderDxfId="62">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D52A48B7-CEB1-4758-9337-93886774715A}" name="No" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{F91F694C-1E9C-43CA-9D38-C2D4125CF031}" name="Tujuan/Kasus" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{1EC3C06F-3680-4E64-943C-9ACFC92F7D7F}" name="Rumus Excel" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{5BD2B065-EDE6-4698-BC9E-106DBEB82066}" name="Penjelasan Singkat" dataDxfId="53"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EB0F2E53-D24D-4DE2-AD4A-03EF9CEB6C0D}" name="Table27" displayName="Table27" ref="A10:H21" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{06477362-F6A6-43F7-B4B5-45B79F94F3A2}" name="No" dataDxfId="18" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C49E30F4-922F-466B-A43D-8A38721E2094}" name="Kolom" dataDxfId="17" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{8721D0AE-8AFD-4E52-B23D-606995225DA9}" name="Masalah" dataDxfId="16" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{4ACA9FBD-6292-4C3A-AA05-D8DFE6141AA8}" name="Jumlah" dataDxfId="15" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{D8C2E810-5BBA-481C-99F4-1031F8127829}" name="sebelum -&gt; sesudah" dataDxfId="14" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{3521876A-DAD5-4DB1-991F-23BAC3EC088A}" name="Tindakan" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{8A0F0C7D-9D0A-4616-9EE9-49D7B7882F2F}" name="Alat Excel" dataDxfId="12" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{9D751B65-471C-47E6-B93B-A451F759E523}" name="Dasar Keputusan" dataDxfId="11" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{EAA21A5F-DCE4-4FD9-A7E9-C9C212FC6047}" name="Table315" displayName="Table315" ref="A24:C35" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7" headerRowCellStyle="Normal 2">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{043E3AC3-2A11-4774-B101-30B7A0658BE5}" name="Kolom" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{DB1CFE93-9DE1-496B-840E-9507880FE0E8}" name="Nilai Kotor" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{17F7FF10-58A4-436A-8A94-E7094C901C09}" name="Nilai Baku" dataDxfId="4" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{84755AD8-B8C6-4E5C-B91B-6FE88BF651DE}" name="Table_Penjualan" displayName="Table_Penjualan" ref="A3:H53" totalsRowShown="0" headerRowDxfId="119">
   <autoFilter ref="A3:H53" xr:uid="{84755AD8-B8C6-4E5C-B91B-6FE88BF651DE}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F8FE5CCB-FA4A-410B-99E9-1B74B9C2B2A2}" name="order_id" dataDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{6C87AA6E-C84E-47EA-9856-6E41252F26CB}" name="tanggal" dataDxfId="141"/>
+    <tableColumn id="1" xr3:uid="{F8FE5CCB-FA4A-410B-99E9-1B74B9C2B2A2}" name="order_id" dataDxfId="118"/>
+    <tableColumn id="2" xr3:uid="{6C87AA6E-C84E-47EA-9856-6E41252F26CB}" name="tanggal" dataDxfId="117"/>
     <tableColumn id="3" xr3:uid="{73A21607-6578-4E98-96C1-FA21D5D5A93E}" name="nama_menu"/>
     <tableColumn id="4" xr3:uid="{9E7F6B7D-26BB-4D23-A32A-E34776939283}" name="kategori"/>
-    <tableColumn id="5" xr3:uid="{6B16A1B2-E30E-4920-A884-123E918D4873}" name="harga_satuan" dataDxfId="140"/>
-    <tableColumn id="6" xr3:uid="{7D3E554E-ED07-4129-845F-65C803384CAD}" name="jumlah_terjual" dataDxfId="139"/>
-    <tableColumn id="7" xr3:uid="{181C617B-D120-4545-813D-8B77DAF521D1}" name="metode_pembayaran" dataDxfId="138"/>
-    <tableColumn id="8" xr3:uid="{B2DCCCE4-1FD2-45ED-B4BD-6DBD2CC7C123}" name="nilai_transaksi" dataDxfId="137">
+    <tableColumn id="5" xr3:uid="{6B16A1B2-E30E-4920-A884-123E918D4873}" name="harga_satuan" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{7D3E554E-ED07-4129-845F-65C803384CAD}" name="jumlah_terjual" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{181C617B-D120-4545-813D-8B77DAF521D1}" name="metode_pembayaran" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{B2DCCCE4-1FD2-45ED-B4BD-6DBD2CC7C123}" name="nilai_transaksi" dataDxfId="113">
       <calculatedColumnFormula>E4*F4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15024,53 +15886,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2D3EB2AF-BFFE-43D6-AAA3-75CDA71579F1}" name="Table10" displayName="Table10" ref="A26:D31" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
-  <autoFilter ref="A26:D31" xr:uid="{2D3EB2AF-BFFE-43D6-AAA3-75CDA71579F1}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3E335885-447E-43F5-AE72-08BEF8FA6E7F}" name="No" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{F3D3347C-AE9F-4B5D-8892-43B69E298AFE}" name="Tujuan/Kasus" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{55F3CDC3-7757-45F3-A3EF-5EA9942A1B50}" name="Rumus Excel" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{C58994CB-6CD9-4EAF-A7EA-6BEB7B73571A}" name="Penjelasan Singkat" dataDxfId="80"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2B43984E-C349-413A-9BFB-A7F32F00FFF1}" name="Table11" displayName="Table11" ref="A35:D39" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
-  <autoFilter ref="A35:D39" xr:uid="{2B43984E-C349-413A-9BFB-A7F32F00FFF1}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{29351D3F-CA74-4483-8825-DBF8EC540217}" name="No" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{A1DEA393-6C32-4DDD-9410-B141231A2055}" name="Tujuan/Kasus" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{A80EEEA2-1401-487A-8432-AE1D5043050C}" name="Rumus Excel" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{01BF720C-419F-44FE-8980-2242B99E4B1F}" name="Penjelasan Singkat" dataDxfId="71"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{188AC7E4-A225-40B6-A5D6-F5E902BF1042}" name="Table3" displayName="Table3" ref="A43:D46" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3" totalsRowBorderDxfId="1">
-  <autoFilter ref="A43:D46" xr:uid="{188AC7E4-A225-40B6-A5D6-F5E902BF1042}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D52A48B7-CEB1-4758-9337-93886774715A}" name="No"/>
-    <tableColumn id="2" xr3:uid="{F91F694C-1E9C-43CA-9D38-C2D4125CF031}" name="Tujuan/Kasus"/>
-    <tableColumn id="3" xr3:uid="{1EC3C06F-3680-4E64-943C-9ACFC92F7D7F}" name="Rumus Excel"/>
-    <tableColumn id="4" xr3:uid="{5BD2B065-EDE6-4698-BC9E-106DBEB82066}" name="Penjelasan Singkat"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D29256BE-A19C-48E7-9D9C-5816237F0390}" name="Table2" displayName="Table2" ref="J3:L8" totalsRowCount="1" headerRowDxfId="136" totalsRowDxfId="133" headerRowBorderDxfId="135" tableBorderDxfId="134" totalsRowBorderDxfId="132">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D29256BE-A19C-48E7-9D9C-5816237F0390}" name="Table2" displayName="Table2" ref="J3:L8" totalsRowCount="1" headerRowDxfId="112" totalsRowDxfId="109" headerRowBorderDxfId="111" tableBorderDxfId="110" totalsRowBorderDxfId="108">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{414BFB58-AA63-4AD2-9478-5D39363BB878}" name="Kategori" totalsRowLabel="Total" totalsRowDxfId="131"/>
-    <tableColumn id="2" xr3:uid="{8EAC0671-BC00-429B-B6DE-B5E730C0597C}" name="Makanan" totalsRowFunction="custom" dataDxfId="130" totalsRowDxfId="129">
+    <tableColumn id="1" xr3:uid="{414BFB58-AA63-4AD2-9478-5D39363BB878}" name="Kategori" totalsRowLabel="Total" totalsRowDxfId="107"/>
+    <tableColumn id="2" xr3:uid="{8EAC0671-BC00-429B-B6DE-B5E730C0597C}" name="Makanan" totalsRowFunction="custom" dataDxfId="106" totalsRowDxfId="105">
       <totalsRowFormula>SUMIF(D4:D53, "Makanan", H4:H53)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9A0E16ED-C118-486A-ACB4-FCBA1E2C0212}" name="Minuman" totalsRowFunction="custom" dataDxfId="128" totalsRowDxfId="127">
+    <tableColumn id="3" xr3:uid="{9A0E16ED-C118-486A-ACB4-FCBA1E2C0212}" name="Minuman" totalsRowFunction="custom" dataDxfId="104" totalsRowDxfId="103">
       <totalsRowFormula>SUMIF(D4:D53, "Minuman", H4:H53)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -15078,18 +15901,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{33231B33-FFA0-4EFB-9D23-764CE0D01DA5}" name="Table4" displayName="Table4" ref="N3:O6" totalsRowShown="0" headerRowDxfId="126" headerRowBorderDxfId="125" tableBorderDxfId="124" totalsRowBorderDxfId="123">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{33231B33-FFA0-4EFB-9D23-764CE0D01DA5}" name="Table4" displayName="Table4" ref="N3:O6" totalsRowShown="0" headerRowDxfId="102" headerRowBorderDxfId="101" tableBorderDxfId="100" totalsRowBorderDxfId="99">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{369968AF-B6CF-4A57-B463-84A3F324DF3C}" name="Kategori" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{3D8BF83A-BA75-4FF5-923E-F607794E3774}" name="Nilai Transaksi" dataDxfId="121"/>
+    <tableColumn id="1" xr3:uid="{369968AF-B6CF-4A57-B463-84A3F324DF3C}" name="Kategori" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{3D8BF83A-BA75-4FF5-923E-F607794E3774}" name="Nilai Transaksi" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{D2703DA7-0E70-485B-BCF1-F2547E8DFC5F}" name="Table16" displayName="Table16" ref="N10:O13" totalsRowShown="0" headerRowDxfId="120" headerRowBorderDxfId="119" tableBorderDxfId="118">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{D2703DA7-0E70-485B-BCF1-F2547E8DFC5F}" name="Table16" displayName="Table16" ref="N10:O13" totalsRowShown="0" headerRowDxfId="96" headerRowBorderDxfId="95" tableBorderDxfId="94">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{35C2EC3C-B01C-4B18-9FCC-4993BCA2F0A1}" name="Kategori"/>
     <tableColumn id="2" xr3:uid="{03082787-5B95-4A2F-9871-FEC96194C79E}" name="Nilai Unit"/>
@@ -15098,64 +15921,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1C3F9945-8DAD-4FA7-A533-FBEB1827C019}" name="Table12" displayName="Table12" ref="A3:C6" totalsRowShown="0" headerRowDxfId="117" dataDxfId="116">
-  <autoFilter ref="A3:C6" xr:uid="{1C3F9945-8DAD-4FA7-A533-FBEB1827C019}"/>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1C3F9945-8DAD-4FA7-A533-FBEB1827C019}" name="Table12" displayName="Table12" ref="A3:C6" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EB654EA0-BF26-4AA0-90CF-4E49BC33CDF8}" name="No" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{A0AB2D48-AEF7-459B-A8DD-0E43877D2DEC}" name="Pertanyaan Bisnis" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{F038965A-A707-4A8C-913C-33610B0A272E}" name="Jawaban" dataDxfId="113"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{50E4DF6B-AC9D-4852-B071-F690B53856AD}" name="Table1214" displayName="Table1214" ref="A11:C17" totalsRowShown="0" headerRowDxfId="112" dataDxfId="111">
-  <autoFilter ref="A11:C17" xr:uid="{50E4DF6B-AC9D-4852-B071-F690B53856AD}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E074270B-E49A-47B9-B49E-66AD2AB5B2F4}" name="No" dataDxfId="110"/>
-    <tableColumn id="2" xr3:uid="{384DA693-1624-4D42-900F-7C12E708E30A}" name="Temuan Data (Insight)" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{976C5065-1234-4A6B-8BEF-E18542270CAF}" name="Rekomendasi Aksi (Action Plan)" dataDxfId="108"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9FAE22C4-446B-4A13-A1CD-0DB87E8C10A0}" name="Table7" displayName="Table7" ref="A2:D5" totalsRowShown="0" dataDxfId="107">
-  <autoFilter ref="A2:D5" xr:uid="{9FAE22C4-446B-4A13-A1CD-0DB87E8C10A0}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F755DA5B-2F83-4385-BCC6-AD508E78DB3A}" name="No" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{8C7CC80E-A128-427F-BD1D-2BACBA719C93}" name="Tujuan/Kasus" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{F1B4465F-FE60-4FF7-B84A-D385948C37B0}" name="Rumus Excel" dataDxfId="104"/>
-    <tableColumn id="4" xr3:uid="{E32FFBC9-7F4D-4672-8A93-DD6EEA3046C8}" name="Penjelasan Singkat" dataDxfId="103"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1D6DB6B6-FE1D-41FB-A522-2B62CD7C9B8B}" name="Table79" displayName="Table79" ref="A9:D14" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
-  <autoFilter ref="A9:D14" xr:uid="{1D6DB6B6-FE1D-41FB-A522-2B62CD7C9B8B}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{36FDD706-320A-4AF4-9DDB-14628E07A8C6}" name="No" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{259F1008-7A90-4BC6-A8CF-3EC2792378BE}" name="Tujuan/Kasus" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{75772802-8B13-4D98-A130-1B1DB609A539}" name="Rumus Excel" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{F29DA025-DBE7-4483-84CB-CEED80B7283F}" name="Penjelasan Singkat" dataDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{EB654EA0-BF26-4AA0-90CF-4E49BC33CDF8}" name="No" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{A0AB2D48-AEF7-459B-A8DD-0E43877D2DEC}" name="Pertanyaan Bisnis" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{F038965A-A707-4A8C-913C-33610B0A272E}" name="Jawaban" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B4D75F84-B8C0-48AC-A1B4-291BA76FEB55}" name="Table9" displayName="Table9" ref="A18:D22" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
-  <autoFilter ref="A18:D22" xr:uid="{924BAF60-657F-4CA9-A658-A358D6D04996}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{625B4CEF-1E36-4695-8BA9-FA81F4574EBE}" name="No" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{C999B219-67E3-4A4F-8146-2F3228023EC0}" name="Tujuan/Kasus" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{7BEBD530-1C27-4A06-B9C4-4750E9600B1D}" name="Rumus Excel" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{FDD7E416-9455-4BB4-9E28-158698304E8A}" name="Penjelasan Singkat" dataDxfId="88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{50E4DF6B-AC9D-4852-B071-F690B53856AD}" name="Table1214" displayName="Table1214" ref="A11:C17" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E074270B-E49A-47B9-B49E-66AD2AB5B2F4}" name="No" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{384DA693-1624-4D42-900F-7C12E708E30A}" name="Temuan Data (Insight)" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{976C5065-1234-4A6B-8BEF-E18542270CAF}" name="Rekomendasi Aksi (Action Plan)" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15459,41 +16241,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599D0F62-F9BB-4438-8550-1AD2D62BE4A8}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -15504,7 +16286,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF19EBF-F1C3-4EF3-BCE0-BBBE41B287AC}">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="74" customWidth="1"/>
     <col min="2" max="2" width="14" style="74" customWidth="1"/>
@@ -15516,7 +16298,7 @@
     <col min="8" max="16384" width="8.6640625" style="74"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
@@ -15539,7 +16321,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="75" t="s">
         <v>7</v>
       </c>
@@ -15553,16 +16335,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" s="75">
         <v>2</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="75" t="s">
         <v>11</v>
       </c>
@@ -15573,7 +16355,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" s="75">
         <v>25000</v>
@@ -15582,10 +16364,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="75" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
         <v>14</v>
       </c>
@@ -15593,7 +16375,7 @@
         <v>46296</v>
       </c>
       <c r="C4" s="75" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D4" s="75" t="s">
         <v>9</v>
@@ -15605,10 +16387,10 @@
         <v>3</v>
       </c>
       <c r="G4" s="75" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
         <v>17</v>
       </c>
@@ -15616,7 +16398,7 @@
         <v>46296</v>
       </c>
       <c r="C5" s="75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D5" s="75" t="s">
         <v>19</v>
@@ -15628,10 +16410,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="75" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
         <v>20</v>
       </c>
@@ -15639,7 +16421,7 @@
         <v>46296</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="75" t="s">
         <v>9</v>
@@ -15654,7 +16436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="75" t="s">
         <v>22</v>
       </c>
@@ -15662,7 +16444,7 @@
         <v>46297</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="75" t="s">
         <v>9</v>
@@ -15677,7 +16459,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="75" t="s">
         <v>23</v>
       </c>
@@ -15688,7 +16470,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" s="75">
         <v>22000</v>
@@ -15700,7 +16482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
         <v>23</v>
       </c>
@@ -15711,7 +16493,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E9" s="75">
         <v>22000</v>
@@ -15723,7 +16505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="75" t="s">
         <v>25</v>
       </c>
@@ -15731,7 +16513,7 @@
         <v>46297</v>
       </c>
       <c r="C10" s="75" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" s="75" t="s">
         <v>9</v>
@@ -15746,7 +16528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="75" t="s">
         <v>26</v>
       </c>
@@ -15754,7 +16536,7 @@
         <v>46297</v>
       </c>
       <c r="C11" s="75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D11" s="75" t="s">
         <v>19</v>
@@ -15766,10 +16548,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>28</v>
       </c>
@@ -15777,13 +16559,13 @@
         <v>46297</v>
       </c>
       <c r="C12" s="75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D12" s="75" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F12" s="75">
         <v>5</v>
@@ -15792,7 +16574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="75" t="s">
         <v>30</v>
       </c>
@@ -15800,7 +16582,7 @@
         <v>46298</v>
       </c>
       <c r="C13" s="75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D13" s="75" t="s">
         <v>9</v>
@@ -15815,7 +16597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
         <v>31</v>
       </c>
@@ -15826,7 +16608,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E14" s="75">
         <v>20000</v>
@@ -15835,18 +16617,18 @@
         <v>3</v>
       </c>
       <c r="G14" s="75" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="75" t="s">
         <v>9</v>
@@ -15861,7 +16643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="75" t="s">
         <v>33</v>
       </c>
@@ -15869,7 +16651,7 @@
         <v>46298</v>
       </c>
       <c r="C16" s="75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D16" s="75" t="s">
         <v>9</v>
@@ -15884,7 +16666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
         <v>34</v>
       </c>
@@ -15907,7 +16689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="75" t="s">
         <v>35</v>
       </c>
@@ -15915,7 +16697,7 @@
         <v>46299</v>
       </c>
       <c r="C18" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" s="75" t="s">
         <v>9</v>
@@ -15930,7 +16712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="75" t="s">
         <v>36</v>
       </c>
@@ -15938,7 +16720,7 @@
         <v>46299</v>
       </c>
       <c r="C19" s="75" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19" s="75" t="s">
         <v>9</v>
@@ -15953,7 +16735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
         <v>37</v>
       </c>
@@ -15970,13 +16752,13 @@
         <v>22000</v>
       </c>
       <c r="F20" s="75" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G20" s="75" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
         <v>38</v>
       </c>
@@ -15987,7 +16769,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="75">
         <v>18000</v>
@@ -15999,12 +16781,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="75" t="s">
         <v>39</v>
       </c>
       <c r="B22" s="75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C22" s="75" t="s">
         <v>21</v>
@@ -16022,7 +16804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="75" t="s">
         <v>40</v>
       </c>
@@ -16030,7 +16812,7 @@
         <v>46300</v>
       </c>
       <c r="C23" s="75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D23" s="75" t="s">
         <v>9</v>
@@ -16045,7 +16827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="75" t="s">
         <v>41</v>
       </c>
@@ -16065,10 +16847,10 @@
         <v>2</v>
       </c>
       <c r="G24" s="75" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="75" t="s">
         <v>42</v>
       </c>
@@ -16091,7 +16873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="75" t="s">
         <v>43</v>
       </c>
@@ -16105,7 +16887,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F26" s="75">
         <v>3</v>
@@ -16114,7 +16896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="75" t="s">
         <v>42</v>
       </c>
@@ -16137,7 +16919,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="75" t="s">
         <v>44</v>
       </c>
@@ -16148,7 +16930,7 @@
         <v>29</v>
       </c>
       <c r="D28" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E28" s="75">
         <v>22000</v>
@@ -16160,7 +16942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="75" t="s">
         <v>45</v>
       </c>
@@ -16177,13 +16959,13 @@
         <v>18000</v>
       </c>
       <c r="F29" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="75" t="s">
         <v>46</v>
       </c>
@@ -16191,7 +16973,7 @@
         <v>46301</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>19</v>
@@ -16206,9 +16988,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="75" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B31" s="76">
         <v>46301</v>
@@ -16229,7 +17011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="75" t="s">
         <v>48</v>
       </c>
@@ -16250,7 +17032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="75" t="s">
         <v>49</v>
       </c>
@@ -16258,7 +17040,7 @@
         <v>46301</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D33" s="75" t="s">
         <v>19</v>
@@ -16273,9 +17055,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="75" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B34" s="76">
         <v>46302</v>
@@ -16287,7 +17069,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="75" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F34" s="75">
         <v>6</v>
@@ -16296,12 +17078,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="75" t="s">
         <v>51</v>
       </c>
       <c r="B35" s="75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="75" t="s">
         <v>12</v>
@@ -16319,7 +17101,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="75" t="s">
         <v>52</v>
       </c>
@@ -16330,7 +17112,7 @@
         <v>27</v>
       </c>
       <c r="D36" s="75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" s="75">
         <v>32000</v>
@@ -16342,7 +17124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="75" t="s">
         <v>53</v>
       </c>
@@ -16359,13 +17141,13 @@
         <v>18000</v>
       </c>
       <c r="F37" s="75" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G37" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="75" t="s">
         <v>54</v>
       </c>
@@ -16385,10 +17167,10 @@
         <v>2</v>
       </c>
       <c r="G38" s="75" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="75" t="s">
         <v>55</v>
       </c>
@@ -16402,7 +17184,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F39" s="75">
         <v>3</v>
@@ -16411,7 +17193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="75" t="s">
         <v>56</v>
       </c>
@@ -16431,10 +17213,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="75" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="75" t="s">
         <v>57</v>
       </c>
@@ -16457,7 +17239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="75" t="s">
         <v>58</v>
       </c>
@@ -16465,7 +17247,7 @@
         <v>46303</v>
       </c>
       <c r="C42" s="75" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D42" s="75" t="s">
         <v>19</v>
@@ -16480,7 +17262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="75" t="s">
         <v>59</v>
       </c>
@@ -16491,7 +17273,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="75" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E43" s="75">
         <v>25000</v>
@@ -16503,7 +17285,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="75" t="s">
         <v>60</v>
       </c>
@@ -16526,7 +17308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="75" t="s">
         <v>61</v>
       </c>
@@ -16549,7 +17331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="75" t="s">
         <v>62</v>
       </c>
@@ -16570,7 +17352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="75" t="s">
         <v>63</v>
       </c>
@@ -16591,7 +17373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="75" t="s">
         <v>64</v>
       </c>
@@ -16605,7 +17387,7 @@
         <v>9</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F48" s="75">
         <v>3</v>
@@ -16614,7 +17396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="75" t="s">
         <v>65</v>
       </c>
@@ -16634,10 +17416,10 @@
         <v>4</v>
       </c>
       <c r="G49" s="75" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="75" t="s">
         <v>66</v>
       </c>
@@ -16654,13 +17436,13 @@
         <v>20000</v>
       </c>
       <c r="F50" s="75" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G50" s="75" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="75" t="s">
         <v>67</v>
       </c>
@@ -16683,7 +17465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="75" t="s">
         <v>68</v>
       </c>
@@ -16706,7 +17488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="75" t="s">
         <v>69</v>
       </c>
@@ -16729,7 +17511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="75" t="s">
         <v>64</v>
       </c>
@@ -16743,7 +17525,7 @@
         <v>9</v>
       </c>
       <c r="E54" s="75" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F54" s="75">
         <v>3</v>
@@ -16759,728 +17541,750 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1789CA9A-C38C-471C-B13A-92C4A2D461FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429F293F-B14D-4442-8D67-A85E247D3C47}">
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26" style="74" customWidth="1"/>
-    <col min="2" max="2" width="20" style="74" customWidth="1"/>
-    <col min="3" max="3" width="34" style="74" customWidth="1"/>
-    <col min="4" max="4" width="12" style="74" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" style="74" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="74" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" style="74" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="74" customWidth="1"/>
     <col min="5" max="6" width="44" style="74" customWidth="1"/>
     <col min="7" max="7" width="30" style="74" customWidth="1"/>
     <col min="8" max="8" width="50" style="74" customWidth="1"/>
     <col min="9" max="16384" width="8.6640625" style="74"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="86" t="s">
-        <v>318</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="79" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="B4" s="82" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="80" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="81">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="132" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="105" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="105"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="131" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="129" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="128">
         <f>COUNTA('02_Data_Kotor'!A2:A54)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="80" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="81">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="129" t="s">
+        <v>302</v>
+      </c>
+      <c r="B6" s="128">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="26.4">
-      <c r="A7" s="80" t="s">
-        <v>313</v>
-      </c>
-      <c r="B7" s="81">
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="127" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="126">
         <f>B5-B6</f>
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="79" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="85" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="105" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="119" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="119" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="119" t="s">
+        <v>296</v>
+      </c>
+      <c r="H10" s="118" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="124">
+        <v>1</v>
+      </c>
+      <c r="B11" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="116" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="123" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" s="116" t="s">
+        <v>368</v>
+      </c>
+      <c r="F11" s="116" t="s">
+        <v>293</v>
+      </c>
+      <c r="G11" s="116" t="s">
+        <v>292</v>
+      </c>
+      <c r="H11" s="115" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="124">
+        <v>2</v>
+      </c>
+      <c r="B12" s="116" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="116" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="123" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" s="116" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="116" t="s">
+        <v>286</v>
+      </c>
+      <c r="G12" s="116" t="s">
+        <v>285</v>
+      </c>
+      <c r="H12" s="115" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="124">
+        <v>3</v>
+      </c>
+      <c r="B13" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="116" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="123" t="s">
+        <v>282</v>
+      </c>
+      <c r="E13" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="F13" s="116" t="s">
+        <v>280</v>
+      </c>
+      <c r="G13" s="116" t="s">
+        <v>279</v>
+      </c>
+      <c r="H13" s="115" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="124">
+        <v>4</v>
+      </c>
+      <c r="B14" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="116" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="123" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" s="116" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="116" t="s">
+        <v>276</v>
+      </c>
+      <c r="G14" s="116" t="s">
+        <v>275</v>
+      </c>
+      <c r="H14" s="115" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="124">
+        <v>5</v>
+      </c>
+      <c r="B15" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="116" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="123" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" s="116" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="116" t="s">
+        <v>270</v>
+      </c>
+      <c r="G15" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="H15" s="115" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="124">
+        <v>6</v>
+      </c>
+      <c r="B16" s="116" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" s="123" t="s">
+        <v>267</v>
+      </c>
+      <c r="E16" s="116" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" s="116" t="s">
+        <v>265</v>
+      </c>
+      <c r="G16" s="116" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="115" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="124">
+        <v>7</v>
+      </c>
+      <c r="B17" s="116" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="116" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" s="123" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" s="116" t="s">
+        <v>260</v>
+      </c>
+      <c r="F17" s="116" t="s">
+        <v>259</v>
+      </c>
+      <c r="G17" s="116" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" s="115" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="124">
+        <v>8</v>
+      </c>
+      <c r="B18" s="116" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="116" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="123" t="s">
+        <v>255</v>
+      </c>
+      <c r="E18" s="116" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="116" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" s="116" t="s">
+        <v>252</v>
+      </c>
+      <c r="H18" s="115" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="124">
+        <v>9</v>
+      </c>
+      <c r="B19" s="116" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="116" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19" s="123" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" s="116" t="s">
+        <v>248</v>
+      </c>
+      <c r="F19" s="116" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="116" t="s">
+        <v>246</v>
+      </c>
+      <c r="H19" s="115" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="124">
+        <v>10</v>
+      </c>
+      <c r="B20" s="116" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="116" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="116" t="s">
+        <v>242</v>
+      </c>
+      <c r="F20" s="116" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="83" t="s">
-        <v>311</v>
-      </c>
-      <c r="D10" s="83" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="83" t="s">
-        <v>309</v>
-      </c>
-      <c r="F10" s="83" t="s">
-        <v>308</v>
-      </c>
-      <c r="G10" s="83" t="s">
-        <v>307</v>
-      </c>
-      <c r="H10" s="83" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="26.4">
-      <c r="A11" s="78">
+      <c r="G20" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="H20" s="115" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="122">
+        <v>11</v>
+      </c>
+      <c r="B21" s="113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="113" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="121" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" s="113" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="113" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21" s="113" t="s">
+        <v>234</v>
+      </c>
+      <c r="H21" s="112" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>370</v>
+      </c>
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="120" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="119" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="118" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="116" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="116" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="116" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="116" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" s="115" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="116" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="116" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="116" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="116" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="115">
         <v>1</v>
       </c>
-      <c r="B11" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>305</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" s="80" t="s">
-        <v>304</v>
-      </c>
-      <c r="F11" s="80" t="s">
-        <v>303</v>
-      </c>
-      <c r="G11" s="80" t="s">
-        <v>302</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="26.4">
-      <c r="A12" s="78">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="113" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="112">
         <v>2</v>
       </c>
-      <c r="B12" s="80" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="80" t="s">
-        <v>299</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>298</v>
-      </c>
-      <c r="E12" s="80" t="s">
-        <v>297</v>
-      </c>
-      <c r="F12" s="80" t="s">
-        <v>296</v>
-      </c>
-      <c r="G12" s="80" t="s">
-        <v>295</v>
-      </c>
-      <c r="H12" s="80" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="26.4">
-      <c r="A13" s="78">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="133" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="133"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="110"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="123">
+        <v>1</v>
+      </c>
+      <c r="B38" s="134" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="111"/>
+      <c r="H38" s="111"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="123">
+        <v>2</v>
+      </c>
+      <c r="B39" s="134" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="111"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="123">
         <v>3</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B40" s="134" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="123">
+        <v>4</v>
+      </c>
+      <c r="B41" s="134" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="123">
+        <v>5</v>
+      </c>
+      <c r="B42" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="123">
+        <v>6</v>
+      </c>
+      <c r="B43" s="134" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="111"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="111"/>
+      <c r="H43" s="111"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="123">
+        <v>7</v>
+      </c>
+      <c r="B44" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="111"/>
+      <c r="H44" s="111"/>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="123">
+        <v>8</v>
+      </c>
+      <c r="B45" s="134" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="111"/>
+      <c r="H45" s="111"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="123">
+        <v>9</v>
+      </c>
+      <c r="B46" s="134" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="111"/>
+      <c r="H46" s="111"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="B48" s="133"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="110"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="123">
         <v>1</v>
       </c>
-      <c r="C13" s="80" t="s">
-        <v>293</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>292</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>291</v>
-      </c>
-      <c r="F13" s="80" t="s">
-        <v>290</v>
-      </c>
-      <c r="G13" s="80" t="s">
-        <v>289</v>
-      </c>
-      <c r="H13" s="80" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="26.4">
-      <c r="A14" s="78">
-        <v>4</v>
-      </c>
-      <c r="B14" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="80" t="s">
-        <v>266</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="80" t="s">
-        <v>287</v>
-      </c>
-      <c r="F14" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="G14" s="80" t="s">
-        <v>285</v>
-      </c>
-      <c r="H14" s="80" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="26.4">
-      <c r="A15" s="78">
-        <v>5</v>
-      </c>
-      <c r="B15" s="80" t="s">
+      <c r="B49" s="134" t="s">
+        <v>215</v>
+      </c>
+      <c r="C49" s="109"/>
+      <c r="D49" s="109"/>
+      <c r="E49" s="109"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="109"/>
+      <c r="H49" s="109"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="123">
         <v>2</v>
       </c>
-      <c r="C15" s="80" t="s">
-        <v>283</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>281</v>
-      </c>
-      <c r="F15" s="80" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="80" t="s">
-        <v>244</v>
-      </c>
-      <c r="H15" s="80" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="78">
-        <v>6</v>
-      </c>
-      <c r="B16" s="80" t="s">
+      <c r="B50" s="134" t="s">
+        <v>214</v>
+      </c>
+      <c r="C50" s="109"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="109"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="109"/>
+      <c r="H50" s="109"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="123">
         <v>3</v>
       </c>
-      <c r="C16" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="80" t="s">
-        <v>276</v>
-      </c>
-      <c r="F16" s="80" t="s">
-        <v>275</v>
-      </c>
-      <c r="G16" s="80" t="s">
-        <v>274</v>
-      </c>
-      <c r="H16" s="80" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="26.4">
-      <c r="A17" s="78">
-        <v>7</v>
-      </c>
-      <c r="B17" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="80" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>271</v>
-      </c>
-      <c r="E17" s="80" t="s">
-        <v>270</v>
-      </c>
-      <c r="F17" s="80" t="s">
-        <v>269</v>
-      </c>
-      <c r="G17" s="80" t="s">
-        <v>268</v>
-      </c>
-      <c r="H17" s="80" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="26.4">
-      <c r="A18" s="78">
-        <v>8</v>
-      </c>
-      <c r="B18" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="80" t="s">
-        <v>266</v>
-      </c>
-      <c r="D18" s="78" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" s="80" t="s">
-        <v>264</v>
-      </c>
-      <c r="F18" s="80" t="s">
-        <v>263</v>
-      </c>
-      <c r="G18" s="80" t="s">
-        <v>262</v>
-      </c>
-      <c r="H18" s="80" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="26.4">
-      <c r="A19" s="78">
-        <v>9</v>
-      </c>
-      <c r="B19" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="E19" s="80" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="80" t="s">
-        <v>257</v>
-      </c>
-      <c r="G19" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="H19" s="80" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="26.4">
-      <c r="A20" s="78">
-        <v>10</v>
-      </c>
-      <c r="B20" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>253</v>
-      </c>
-      <c r="E20" s="80" t="s">
-        <v>252</v>
-      </c>
-      <c r="F20" s="80" t="s">
-        <v>251</v>
-      </c>
-      <c r="G20" s="80" t="s">
-        <v>250</v>
-      </c>
-      <c r="H20" s="80" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="26.4">
-      <c r="A21" s="78">
-        <v>11</v>
-      </c>
-      <c r="B21" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="D21" s="78" t="s">
-        <v>247</v>
-      </c>
-      <c r="E21" s="80" t="s">
-        <v>246</v>
-      </c>
-      <c r="F21" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" s="80" t="s">
-        <v>244</v>
-      </c>
-      <c r="H21" s="80" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="79" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="83" t="s">
-        <v>241</v>
-      </c>
-      <c r="B24" s="83" t="s">
-        <v>240</v>
-      </c>
-      <c r="C24" s="83" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="80" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="80" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="80" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="80" t="s">
-        <v>217</v>
-      </c>
-      <c r="C29" s="80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="80" t="s">
-        <v>237</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="80" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="80" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="80" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="80" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="C33" s="80" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="80" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" s="84">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="79" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1">
-      <c r="A38" s="78">
-        <v>1</v>
-      </c>
-      <c r="B38" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
-      <c r="H38" s="88"/>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1">
-      <c r="A39" s="78">
-        <v>2</v>
-      </c>
-      <c r="B39" s="88" t="s">
-        <v>233</v>
-      </c>
-      <c r="C39" s="88"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="88"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1">
-      <c r="A40" s="78">
-        <v>3</v>
-      </c>
-      <c r="B40" s="88" t="s">
-        <v>232</v>
-      </c>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-    </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1">
-      <c r="A41" s="78">
-        <v>4</v>
-      </c>
-      <c r="B41" s="88" t="s">
-        <v>231</v>
-      </c>
-      <c r="C41" s="88"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="88"/>
-      <c r="H41" s="88"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1">
-      <c r="A42" s="78">
-        <v>5</v>
-      </c>
-      <c r="B42" s="88" t="s">
-        <v>230</v>
-      </c>
-      <c r="C42" s="88"/>
-      <c r="D42" s="88"/>
-      <c r="E42" s="88"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="88"/>
-      <c r="H42" s="88"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1">
-      <c r="A43" s="78">
-        <v>6</v>
-      </c>
-      <c r="B43" s="88" t="s">
-        <v>229</v>
-      </c>
-      <c r="C43" s="88"/>
-      <c r="D43" s="88"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="88"/>
-      <c r="G43" s="88"/>
-      <c r="H43" s="88"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1">
-      <c r="A44" s="78">
-        <v>7</v>
-      </c>
-      <c r="B44" s="88" t="s">
-        <v>228</v>
-      </c>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="88"/>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1">
-      <c r="A45" s="78">
-        <v>8</v>
-      </c>
-      <c r="B45" s="88" t="s">
-        <v>227</v>
-      </c>
-      <c r="C45" s="88"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
-      <c r="F45" s="88"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="88"/>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1">
-      <c r="A46" s="78">
-        <v>9</v>
-      </c>
-      <c r="B46" s="88" t="s">
-        <v>226</v>
-      </c>
-      <c r="C46" s="88"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="88"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="88"/>
-      <c r="H46" s="88"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="79" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1">
-      <c r="A49" s="78">
-        <v>1</v>
-      </c>
-      <c r="B49" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="C49" s="88"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="88"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1">
-      <c r="A50" s="78">
-        <v>2</v>
-      </c>
-      <c r="B50" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" s="88"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="88"/>
-      <c r="H50" s="88"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1">
-      <c r="A51" s="78">
-        <v>3</v>
-      </c>
-      <c r="B51" s="88" t="s">
-        <v>222</v>
-      </c>
-      <c r="C51" s="88"/>
-      <c r="D51" s="88"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="88"/>
-      <c r="H51" s="88"/>
+      <c r="B51" s="134" t="s">
+        <v>213</v>
+      </c>
+      <c r="C51" s="109"/>
+      <c r="D51" s="109"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="109"/>
+      <c r="G51" s="109"/>
+      <c r="H51" s="109"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B45:H45"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A48:B48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB47AA87-DFD7-4834-83B0-0F0D6AF121D0}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -17500,30 +18304,30 @@
     <col min="16" max="16" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="J2" s="93" t="s">
-        <v>328</v>
-      </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="N2" s="93" t="s">
-        <v>203</v>
-      </c>
-      <c r="O2" s="93"/>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J2" s="96" t="s">
+        <v>314</v>
+      </c>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="N2" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="O2" s="96"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -17561,10 +18365,10 @@
         <v>82</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -17610,7 +18414,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -17656,7 +18460,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -17683,7 +18487,7 @@
         <v>75000</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="K6" s="14">
         <f>AVERAGEIFS(H4:H53, D4:D53, "Makanan")</f>
@@ -17702,7 +18506,7 @@
         <v>57560</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -17729,7 +18533,7 @@
         <v>40000</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="K7" s="25">
         <f>SUMIF(D4:D53, "Makanan", H4:H53) / COUNTIF(D4:D53, "Makanan")</f>
@@ -17741,7 +18545,7 @@
       </c>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -17768,7 +18572,7 @@
         <v>56000</v>
       </c>
       <c r="J8" s="65" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="K8" s="66">
         <f>SUMIF(D4:D53, "Makanan", H4:H53)</f>
@@ -17779,7 +18583,7 @@
         <v>2112000</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -17805,13 +18609,13 @@
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="N9" s="92" t="s">
-        <v>205</v>
-      </c>
-      <c r="O9" s="92"/>
+      <c r="N9" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="O9" s="95"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1">
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -17837,20 +18641,20 @@
         <f t="shared" si="0"/>
         <v>22000</v>
       </c>
-      <c r="J10" s="94" t="s">
-        <v>204</v>
-      </c>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
+      <c r="J10" s="97" t="s">
+        <v>195</v>
+      </c>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
       <c r="N10" s="71" t="s">
         <v>82</v>
       </c>
       <c r="O10" s="72" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="P10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+    <row r="11" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -17886,7 +18690,7 @@
         <v>81</v>
       </c>
       <c r="N11" s="70" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O11" s="69">
         <f>MAX(F4:F53)</f>
@@ -17894,7 +18698,7 @@
       </c>
       <c r="P11" s="12"/>
     </row>
-    <row r="12" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+    <row r="12" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -17933,7 +18737,7 @@
         <v/>
       </c>
       <c r="N12" s="70" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="O12" s="69">
         <f>MIN(F4:F53)</f>
@@ -17941,7 +18745,7 @@
       </c>
       <c r="P12" s="12"/>
     </row>
-    <row r="13" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+    <row r="13" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -17979,14 +18783,14 @@
         <v/>
       </c>
       <c r="N13" s="30" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="O13" s="30">
         <f>AVERAGE(F4:F53)</f>
         <v>2.48</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+    <row r="14" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -18023,11 +18827,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-    </row>
-    <row r="15" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -18065,7 +18869,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.6" thickTop="1" thickBot="1">
+    <row r="16" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -18103,7 +18907,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="17" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -18141,7 +18945,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="18" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -18179,7 +18983,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="19" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -18217,7 +19021,7 @@
         <v>Es Kopi Susu</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" thickTop="1">
+    <row r="20" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -18244,7 +19048,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1">
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -18270,12 +19074,12 @@
         <f t="shared" si="0"/>
         <v>44000</v>
       </c>
-      <c r="J21" s="89" t="s">
-        <v>206</v>
-      </c>
-      <c r="K21" s="89"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+      <c r="J21" s="92" t="s">
+        <v>197</v>
+      </c>
+      <c r="K21" s="92"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>38</v>
       </c>
@@ -18309,7 +19113,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="23" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
@@ -18343,7 +19147,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="24" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -18370,7 +19174,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="25" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -18397,14 +19201,14 @@
         <v>40000</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="K25" s="29">
         <f>MAX(K12:K19)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="26" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -18431,14 +19235,14 @@
         <v>50000</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="K26" s="29">
         <f>MIN(K12:K19)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="27" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
@@ -18465,14 +19269,14 @@
         <v>96000</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="K27" s="105">
+        <v>333</v>
+      </c>
+      <c r="K27" s="84">
         <f>AVERAGE(K12:K19)</f>
         <v>15.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" thickTop="1">
+    <row r="28" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
@@ -18500,7 +19304,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1">
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
@@ -18527,7 +19331,7 @@
         <v>54000</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="30" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -18554,14 +19358,14 @@
         <v>44000</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="K30" s="101">
+        <v>327</v>
+      </c>
+      <c r="K30" s="80">
         <f>IFERROR(GETPIVOTDATA("Sum of nilai_transaksi",'04_Pivot_Table'!$D$1),0)</f>
         <v>2878000</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="31" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>47</v>
       </c>
@@ -18588,14 +19392,14 @@
         <v>84000</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="K31" s="102">
+        <v>328</v>
+      </c>
+      <c r="K31" s="81">
         <f>IFERROR(GETPIVOTDATA("Count of order_id",'04_Pivot_Table'!$J$4),0)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.6" thickTop="1" thickBot="1">
+    <row r="32" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -18622,14 +19426,14 @@
         <v>25000</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="K32" s="103">
+        <v>329</v>
+      </c>
+      <c r="K32" s="82">
         <f>IFERROR(GETPIVOTDATA("Sum of jumlah_terjual",'04_Pivot_Table'!$A$1),0)</f>
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.6" thickTop="1" thickBot="1">
+    <row r="33" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>49</v>
       </c>
@@ -18656,14 +19460,14 @@
         <v>80000</v>
       </c>
       <c r="J33" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="K33" s="104">
+        <v>330</v>
+      </c>
+      <c r="K33" s="83">
         <f>IFERROR(GETPIVOTDATA("Average of nilai_transaksi",'04_Pivot_Table'!$G$1),0)</f>
         <v>57560</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" thickTop="1">
+    <row r="34" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -18690,7 +19494,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -18717,7 +19521,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>52</v>
       </c>
@@ -18744,7 +19548,7 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>53</v>
       </c>
@@ -18771,7 +19575,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
@@ -18798,7 +19602,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>55</v>
       </c>
@@ -18825,7 +19629,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>56</v>
       </c>
@@ -18852,7 +19656,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
@@ -18879,7 +19683,7 @@
         <v>88000</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>58</v>
       </c>
@@ -18906,7 +19710,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>59</v>
       </c>
@@ -18933,7 +19737,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
@@ -18960,7 +19764,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
@@ -18987,7 +19791,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
@@ -19014,7 +19818,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
@@ -19041,7 +19845,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>64</v>
       </c>
@@ -19068,7 +19872,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>65</v>
       </c>
@@ -19095,7 +19899,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>66</v>
       </c>
@@ -19122,7 +19926,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>67</v>
       </c>
@@ -19149,7 +19953,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
@@ -19176,7 +19980,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>69</v>
       </c>
@@ -19232,7 +20036,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8675E8-99ED-486B-913F-0B2D90A49294}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -19244,7 +20048,7 @@
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>76</v>
       </c>
@@ -19264,7 +20068,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
@@ -19284,7 +20088,7 @@
         <v>47875</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>27</v>
       </c>
@@ -19304,7 +20108,7 @@
         <v>62117.647058823532</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
@@ -19330,7 +20134,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -19344,7 +20148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
@@ -19358,7 +20162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -19384,7 +20188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
@@ -19410,7 +20214,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
@@ -19430,7 +20234,7 @@
         <v>2.7058823529411766</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>77</v>
       </c>
@@ -19450,7 +20254,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>76</v>
       </c>
@@ -19464,8 +20268,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="100">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="79">
         <v>46296</v>
       </c>
       <c r="B14" s="2">
@@ -19478,8 +20282,8 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="100">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="79">
         <v>46297</v>
       </c>
       <c r="B15" s="2">
@@ -19492,8 +20296,8 @@
         <v>280000</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="100">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="79">
         <v>46298</v>
       </c>
       <c r="B16" s="2">
@@ -19506,8 +20310,8 @@
         <v>288000</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="100">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="79">
         <v>46299</v>
       </c>
       <c r="B17" s="2">
@@ -19520,8 +20324,8 @@
         <v>325000</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="100">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="79">
         <v>46300</v>
       </c>
       <c r="B18" s="2">
@@ -19534,8 +20338,8 @@
         <v>336000</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="100">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="79">
         <v>46301</v>
       </c>
       <c r="B19" s="2">
@@ -19548,8 +20352,8 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="100">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="79">
         <v>46302</v>
       </c>
       <c r="B20" s="2">
@@ -19562,8 +20366,8 @@
         <v>475000</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="100">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="79">
         <v>46303</v>
       </c>
       <c r="B21" s="2">
@@ -19576,8 +20380,8 @@
         <v>616000</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="100">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="79">
         <v>46304</v>
       </c>
       <c r="B22" s="2">
@@ -19590,15 +20394,15 @@
         <v>2878000</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="100">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="79">
         <v>46305</v>
       </c>
       <c r="B23" s="2">
         <v>278000</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="73" t="s">
         <v>77</v>
       </c>
@@ -19614,60 +20418,63 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4886C23-20E7-4C65-8439-9304AA81F199}">
-  <dimension ref="B1:AD6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:AF6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="98"/>
+    <col min="1" max="16384" width="8.88671875" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:30" ht="24" customHeight="1">
-      <c r="B1" s="99" t="s">
+    <row r="1" spans="2:32" s="106" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
-      <c r="AC1" s="99"/>
-      <c r="AD1" s="99"/>
-    </row>
-    <row r="2" spans="2:30" ht="19.95" customHeight="1"/>
-    <row r="3" spans="2:30" ht="19.95" customHeight="1"/>
-    <row r="4" spans="2:30" ht="19.95" customHeight="1"/>
-    <row r="5" spans="2:30" ht="19.95" customHeight="1"/>
-    <row r="6" spans="2:30" ht="72" customHeight="1"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
+      <c r="AC1" s="107"/>
+      <c r="AD1" s="107"/>
+      <c r="AE1" s="107"/>
+      <c r="AF1" s="107"/>
+    </row>
+    <row r="2" spans="2:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:32" ht="72" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="B1:AF1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -19677,22 +20484,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F8D2DE-EE40-4922-BEDD-94D3284B611B}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="51.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-    </row>
-    <row r="2" spans="1:3" ht="13.2" customHeight="1"/>
-    <row r="3" spans="1:3" ht="33" customHeight="1">
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+    </row>
+    <row r="2" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>93</v>
       </c>
@@ -19703,7 +20510,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="38.4" customHeight="1">
+    <row r="4" spans="1:3" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -19715,7 +20522,7 @@
         <v>Es Kopi Susu</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -19727,7 +20534,7 @@
         <v>2112000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28.8">
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -19739,14 +20546,14 @@
         <v>57560</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18">
-      <c r="A9" s="90" t="s">
+    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="63" t="s">
         <v>93</v>
       </c>
@@ -19757,105 +20564,106 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="90.6" customHeight="1">
+    <row r="12" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="62">
         <v>1</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>184</v>
+        <v>357</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="72">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="62">
         <v>2</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="72">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="62">
         <v>3</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>189</v>
+        <v>361</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="57.6">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="62">
         <v>4</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>190</v>
+        <v>363</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="105" customHeight="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="62">
         <v>5</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="129.6">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="134.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="62">
         <v>6</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>326</v>
+        <v>366</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18">
-      <c r="A19" s="90" t="s">
-        <v>193</v>
-      </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-    </row>
-    <row r="20" spans="1:3" ht="20.399999999999999" customHeight="1">
-      <c r="A20" s="5">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:3" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="92" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+    </row>
+    <row r="20" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="57">
         <v>1</v>
       </c>
-      <c r="B20" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="96"/>
-    </row>
-    <row r="21" spans="1:3" ht="30" customHeight="1">
-      <c r="A21" s="5">
+      <c r="B20" s="104" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="104"/>
+    </row>
+    <row r="21" spans="1:3" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="57">
         <v>2</v>
       </c>
-      <c r="B21" s="96" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="96"/>
-    </row>
-    <row r="22" spans="1:3" ht="40.200000000000003" customHeight="1">
-      <c r="A22" s="5">
+      <c r="B21" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="104"/>
+    </row>
+    <row r="22" spans="1:3" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="57">
         <v>3</v>
       </c>
-      <c r="B22" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="C22" s="96"/>
+      <c r="B22" s="104" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -19878,22 +20686,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924BAF60-657F-4CA9-A658-A358D6D04996}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
     <col min="4" max="4" width="47.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6">
-      <c r="A1" s="114" t="s">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>93</v>
       </c>
@@ -19907,7 +20715,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>1</v>
       </c>
@@ -19915,27 +20723,27 @@
         <v>97</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="57">
         <v>2</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.8">
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="57">
         <v>3</v>
       </c>
@@ -19943,21 +20751,21 @@
         <v>98</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.6">
-      <c r="A8" s="112" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>93</v>
       </c>
@@ -19971,7 +20779,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="57">
         <v>4</v>
       </c>
@@ -19979,27 +20787,27 @@
         <v>101</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="57">
         <v>5</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.8">
+    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="57">
         <v>6</v>
       </c>
@@ -20007,13 +20815,13 @@
         <v>102</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8">
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="57">
         <v>7</v>
       </c>
@@ -20021,13 +20829,13 @@
         <v>103</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8">
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="57">
         <v>8</v>
       </c>
@@ -20035,21 +20843,21 @@
         <v>104</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6">
-      <c r="A17" s="113" t="s">
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
         <v>93</v>
       </c>
@@ -20063,7 +20871,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28.8">
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>9</v>
       </c>
@@ -20071,13 +20879,13 @@
         <v>116</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D19" s="60" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.8">
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>10</v>
       </c>
@@ -20085,27 +20893,27 @@
         <v>115</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="28.8">
+    <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>11</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.8">
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>12</v>
       </c>
@@ -20113,21 +20921,21 @@
         <v>114</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.6">
-      <c r="A25" s="112" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="100" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="112"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="55" t="s">
         <v>93</v>
       </c>
@@ -20141,7 +20949,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8">
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>13</v>
       </c>
@@ -20149,13 +20957,13 @@
         <v>118</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D27" s="61" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="28.8">
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>14</v>
       </c>
@@ -20163,13 +20971,13 @@
         <v>119</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>15</v>
       </c>
@@ -20177,27 +20985,27 @@
         <v>120</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="D29" s="44" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>16</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D30" s="43" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="28.8">
+    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <v>17</v>
       </c>
@@ -20205,21 +21013,21 @@
         <v>124</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.6">
-      <c r="A34" s="112" t="s">
-        <v>339</v>
-      </c>
-      <c r="B34" s="112"/>
-      <c r="C34" s="112"/>
-      <c r="D34" s="112"/>
-    </row>
-    <row r="35" spans="1:4">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="100" t="s">
+        <v>325</v>
+      </c>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="50" t="s">
         <v>93</v>
       </c>
@@ -20233,7 +21041,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="48">
         <v>18</v>
       </c>
@@ -20241,13 +21049,13 @@
         <v>125</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D36" s="60" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="49">
         <v>19</v>
       </c>
@@ -20255,13 +21063,13 @@
         <v>126</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="28.8">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="48">
         <v>20</v>
       </c>
@@ -20269,13 +21077,13 @@
         <v>127</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="D38" s="46" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="28.8">
+    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="52">
         <v>21</v>
       </c>
@@ -20283,21 +21091,21 @@
         <v>128</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.6">
-      <c r="A42" s="112" t="s">
-        <v>348</v>
-      </c>
-      <c r="B42" s="112"/>
-      <c r="C42" s="112"/>
-      <c r="D42" s="112"/>
-    </row>
-    <row r="43" spans="1:4">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="100" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" s="100"/>
+      <c r="C42" s="100"/>
+      <c r="D42" s="100"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="50" t="s">
         <v>93</v>
       </c>
@@ -20311,96 +21119,96 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="28.8">
+    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="48">
         <v>22</v>
       </c>
       <c r="B44" s="46" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="D44" s="60" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="43.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="49">
         <v>23</v>
       </c>
       <c r="B45" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="D45" s="47" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="88">
+        <v>24</v>
+      </c>
+      <c r="B46" s="89" t="s">
+        <v>337</v>
+      </c>
+      <c r="C46" s="90" t="s">
+        <v>338</v>
+      </c>
+      <c r="D46" s="89" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="100" t="s">
         <v>350</v>
       </c>
-      <c r="C45" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="D45" s="47" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="28.8">
-      <c r="A46" s="109">
-        <v>24</v>
-      </c>
-      <c r="B46" s="110" t="s">
-        <v>351</v>
-      </c>
-      <c r="C46" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="D46" s="110" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.6">
-      <c r="A49" s="112" t="s">
-        <v>364</v>
-      </c>
-      <c r="B49" s="112"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="106" t="s">
+      <c r="B49" s="100"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="100"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="107" t="s">
+      <c r="B50" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="107" t="s">
+      <c r="C50" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="108" t="s">
+      <c r="D50" s="87" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="28.8">
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>25</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D51" s="61" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="43.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>26</v>
       </c>
       <c r="B52" s="47" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
